--- a/Denmark_wedding_municipalities_2026.xlsx
+++ b/Denmark_wedding_municipalities_2026.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Municipalities" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Agencies" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Municipalities'!$A$1:$N$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Municipalities'!$A$1:$R$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -119,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -160,6 +161,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -527,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -583,7 +590,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>COUNTIF(Municipalities!J:J,A5)</f>
+        <f>COUNTIF(Municipalities!N:N,A5)</f>
         <v/>
       </c>
       <c r="C5" s="2" t="n"/>
@@ -596,7 +603,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF(Municipalities!J:J,A6)</f>
+        <f>COUNTIF(Municipalities!N:N,A6)</f>
         <v/>
       </c>
       <c r="C6" s="2" t="n"/>
@@ -609,7 +616,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>COUNTIF(Municipalities!J:J,A7)</f>
+        <f>COUNTIF(Municipalities!N:N,A7)</f>
         <v/>
       </c>
       <c r="C7" s="2" t="n"/>
@@ -622,7 +629,7 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIF(Municipalities!J:J,A8)</f>
+        <f>COUNTIF(Municipalities!N:N,A8)</f>
         <v/>
       </c>
       <c r="C8" s="2" t="n"/>
@@ -635,7 +642,7 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIF(Municipalities!J:J,A9)</f>
+        <f>COUNTIF(Municipalities!N:N,A9)</f>
         <v/>
       </c>
       <c r="C9" s="2" t="n"/>
@@ -648,7 +655,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIF(Municipalities!J:J,A10)</f>
+        <f>COUNTIF(Municipalities!N:N,A10)</f>
         <v/>
       </c>
       <c r="C10" s="2" t="n"/>
@@ -745,7 +752,7 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Possible: no rule or reported backlog blocks a date in the window; availability itself is unconfirmed.</t>
+          <t>Main switchboard phone / email / address / contact page were collected from each municipality's own contact page via search summaries on 17 Sep 2026. Wedding-office contacts are listed separately where one was found.</t>
         </is>
       </c>
       <c r="B19" s="2" t="n"/>
@@ -755,7 +762,7 @@
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Possible (low confidence): same, but based on thinner evidence.</t>
+          <t>Possible: no rule or reported backlog blocks a date in the window; availability itself is unconfirmed.</t>
         </is>
       </c>
       <c r="B20" s="2" t="n"/>
@@ -765,7 +772,7 @@
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Unknown: researched, but no waiting-time information found.</t>
+          <t>Possible (low confidence): same, but based on thinner evidence.</t>
         </is>
       </c>
       <c r="B21" s="2" t="n"/>
@@ -775,7 +782,7 @@
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Unknown (not researched): the automated search quota ran out before this municipality was reached; only the official website is listed.</t>
+          <t>Unknown: researched, but no waiting-time information found.</t>
         </is>
       </c>
       <c r="B22" s="2" t="n"/>
@@ -785,7 +792,7 @@
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Unlikely: a stated lead time, limited ceremony days or a reported backlog makes the window improbable.</t>
+          <t>Unknown (not researched): the automated search quota ran out before this municipality was reached; only the official website is listed.</t>
         </is>
       </c>
       <c r="B23" s="2" t="n"/>
@@ -795,7 +802,7 @@
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>No: the municipality's own rule or reply rules the window out (e.g. earliest date 14 days after the certificate arrives).</t>
+          <t>Unlikely: a stated lead time, limited ceremony days or a reported backlog makes the window improbable.</t>
         </is>
       </c>
       <c r="B24" s="2" t="n"/>
@@ -805,7 +812,7 @@
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Chance column assumes the Familieretshuset certificate arrives 25-29 September. Email/phone: dial +45 before Danish numbers.</t>
+          <t>No: the municipality's own rule or reply rules the window out (e.g. earliest date 14 days after the certificate arrives).</t>
         </is>
       </c>
       <c r="B25" s="2" t="n"/>
@@ -815,16 +822,27 @@
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Transport times are approximate. CPH = Copenhagen Airport, BLL = Billund, AAR = Aarhus, AAL = Aalborg, HAM = Hamburg.</t>
+          <t>Chance column assumes the Familieretshuset certificate arrives 25-29 September. Email/phone: dial +45 before Danish numbers.</t>
         </is>
       </c>
       <c r="B26" s="2" t="n"/>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n"/>
     </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Transport times are approximate. CPH = Copenhagen Airport, BLL = Billund, AAR = Aarhus, AAL = Aalborg, HAM = Hamburg.</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A21:D21"/>
@@ -844,7 +862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N99"/>
+  <dimension ref="A1:R99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -854,13 +872,17 @@
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="42" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -896,40 +918,60 @@
       </c>
       <c r="G1" s="10" t="inlineStr">
         <is>
-          <t>Email / phone</t>
+          <t>Wedding office email / phone (if found)</t>
         </is>
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
+          <t>Main switchboard phone</t>
+        </is>
+      </c>
+      <c r="I1" s="10" t="inlineStr">
+        <is>
+          <t>Main municipal email</t>
+        </is>
+      </c>
+      <c r="J1" s="10" t="inlineStr">
+        <is>
+          <t>Town hall address</t>
+        </is>
+      </c>
+      <c r="K1" s="10" t="inlineStr">
+        <is>
+          <t>Contact page</t>
+        </is>
+      </c>
+      <c r="L1" s="10" t="inlineStr">
+        <is>
           <t>Ceremony days</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>Availability / lead time</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>Chance of a date 28 Sep - 7 Oct 2026</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>Transport from London (approx.)</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="P1" s="10" t="inlineStr">
         <is>
           <t>Official website</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="Q1" s="10" t="inlineStr">
         <is>
           <t>Wedding page</t>
         </is>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="R1" s="10" t="inlineStr">
         <is>
           <t>Notes and sources</t>
         </is>
@@ -967,35 +1009,51 @@
       </c>
       <c r="H2" s="11" t="inlineStr">
         <is>
+          <t>+45 43 68 68 68</t>
+        </is>
+      </c>
+      <c r="I2" s="11" t="inlineStr">
+        <is>
+          <t>borgerogydelsescenter@albertslund.dk</t>
+        </is>
+      </c>
+      <c r="J2" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K2" s="11" t="inlineStr"/>
+      <c r="L2" s="11" t="inlineStr">
+        <is>
           <t>Mon-Fri 10-14 (Thu to 16); 1st Saturday of month 11-14 (Sat 3 Oct falls in window; own witnesses on Sat)</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr">
+      <c r="M2" s="11" t="inlineStr">
         <is>
           <t>No waiting time published; office proposes a day if you have no preference</t>
         </is>
       </c>
-      <c r="J2" s="13" t="inlineStr">
+      <c r="N2" s="13" t="inlineStr">
         <is>
           <t>Possible</t>
         </is>
       </c>
-      <c r="K2" s="11" t="inlineStr">
+      <c r="O2" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to København H 15 min, S-train line B to Albertslund 20 min.</t>
         </is>
       </c>
-      <c r="L2" s="14" t="inlineStr">
+      <c r="P2" s="14" t="inlineStr">
         <is>
           <t>https://albertslund.dk</t>
         </is>
       </c>
-      <c r="M2" s="14" t="inlineStr">
+      <c r="Q2" s="14" t="inlineStr">
         <is>
           <t>https://albertslund.dk/voksne-og-aeldre/vielse-oekonomi-og-stoette/vielse/vies-paa-raadhuset</t>
         </is>
       </c>
-      <c r="N2" s="11" t="inlineStr">
+      <c r="R2" s="11" t="inlineStr">
         <is>
           <t>Marry Abroad Simply lists Albertslund Rådhus as a venue it uses for international couples. Six possible days in window.</t>
         </is>
@@ -1033,31 +1091,51 @@
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
+          <t>43 28 28 28</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>borgerservice@brondby.dk</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="inlineStr">
+        <is>
+          <t>Brøndby Rådhus, Park Allé 160, 2605 Brøndby</t>
+        </is>
+      </c>
+      <c r="K3" s="14" t="inlineStr">
+        <is>
+          <t>https://www.brondby.dk/om-kommunen/kontakt-og-abningstider</t>
+        </is>
+      </c>
+      <c r="L3" s="11" t="inlineStr">
+        <is>
           <t>not found (dedicated wedding inbox exists)</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="M3" s="11" t="inlineStr">
         <is>
           <t>No waiting time published</t>
         </is>
       </c>
-      <c r="J3" s="13" t="inlineStr">
+      <c r="N3" s="13" t="inlineStr">
         <is>
           <t>Possible</t>
         </is>
       </c>
-      <c r="K3" s="11" t="inlineStr">
+      <c r="O3" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. S-train to Brøndbyøster/Glostrup approx 25 min.</t>
         </is>
       </c>
-      <c r="L3" s="14" t="inlineStr">
+      <c r="P3" s="14" t="inlineStr">
         <is>
           <t>https://www.brondby.dk</t>
         </is>
       </c>
-      <c r="M3" s="11" t="inlineStr"/>
-      <c r="N3" s="11" t="inlineStr">
+      <c r="Q3" s="11" t="inlineStr"/>
+      <c r="R3" s="11" t="inlineStr">
         <is>
           <t>Sweep found the wedding mailbox but no schedule. Ask directly.</t>
         </is>
@@ -1095,31 +1173,51 @@
       </c>
       <c r="H4" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>7235 4000</t>
         </is>
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
+          <t>borgerservice@furesoe.dk</t>
+        </is>
+      </c>
+      <c r="J4" s="11" t="inlineStr">
+        <is>
+          <t>Furesø Kommune, Rådhustorvet 2, 3520 Farum</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
+        <is>
+          <t>https://www.furesoe.dk/om-kommunen/kontakt-og-akutnumre/kontakt-administrationen</t>
+        </is>
+      </c>
+      <c r="L4" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M4" s="11" t="inlineStr">
+        <is>
           <t>Municipality states no waiting time</t>
         </is>
       </c>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="N4" s="13" t="inlineStr">
         <is>
           <t>Possible</t>
         </is>
       </c>
-      <c r="K4" s="11" t="inlineStr">
+      <c r="O4" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. S-train to Farum or Værløse approx 30 min.</t>
         </is>
       </c>
-      <c r="L4" s="14" t="inlineStr">
+      <c r="P4" s="14" t="inlineStr">
         <is>
           <t>https://www.furesoe.dk</t>
         </is>
       </c>
-      <c r="M4" s="11" t="inlineStr"/>
-      <c r="N4" s="11" t="inlineStr">
+      <c r="Q4" s="11" t="inlineStr"/>
+      <c r="R4" s="11" t="inlineStr">
         <is>
           <t>Sweep: no waiting time and no residency bar found.</t>
         </is>
@@ -1157,35 +1255,51 @@
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
+          <t>+45 72 49 60 00</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>borgerservice@gribskov.dk</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr"/>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
           <t>not found; registrar can marry at town hall or elsewhere</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Book up to 4 months ahead; no waiting time published</t>
         </is>
       </c>
-      <c r="J5" s="13" t="inlineStr">
+      <c r="N5" s="13" t="inlineStr">
         <is>
           <t>Possible</t>
         </is>
       </c>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="O5" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to Hillerød then local train to Helsinge, approx 1h15.</t>
         </is>
       </c>
-      <c r="L5" s="14" t="inlineStr">
+      <c r="P5" s="14" t="inlineStr">
         <is>
           <t>https://gribskov.dk</t>
         </is>
       </c>
-      <c r="M5" s="14" t="inlineStr">
+      <c r="Q5" s="14" t="inlineStr">
         <is>
           <t>https://gribskov.dk/borger/borgerservice/vielse/vielse-paa-raadhuset-andre-steder-eller-i-kirken</t>
         </is>
       </c>
-      <c r="N5" s="11" t="inlineStr">
+      <c r="R5" s="11" t="inlineStr">
         <is>
           <t>Explicit page for international couples: email desired date plus certificate.</t>
         </is>
@@ -1223,31 +1337,51 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
+          <t>+45 49 28 28 28</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>borgerservice@helsingor.dk</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>Stengade 59, Helsingør (rådhus); Borgerservice: Birkedalsvej 27, 3000 Helsingør</t>
+        </is>
+      </c>
+      <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>https://www.helsingor.dk/nyheder-og-fakta/kontakt-helsingoer-kommune</t>
+        </is>
+      </c>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
           <t>not found (agencies list it as a venue)</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="M6" s="11" t="inlineStr">
         <is>
           <t>You state a desired date in the declaration and Borgerservice confirms</t>
         </is>
       </c>
-      <c r="J6" s="13" t="inlineStr">
+      <c r="N6" s="13" t="inlineStr">
         <is>
           <t>Possible</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="O6" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to Helsingør approx 45 min.</t>
         </is>
       </c>
-      <c r="L6" s="14" t="inlineStr">
+      <c r="P6" s="14" t="inlineStr">
         <is>
           <t>https://www.helsingor.dk</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr">
+      <c r="Q6" s="11" t="inlineStr"/>
+      <c r="R6" s="11" t="inlineStr">
         <is>
           <t>Agencies work with Helsingør for international couples.</t>
         </is>
@@ -1285,35 +1419,51 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
+          <t>+45 76 29 21 25</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>borgerservice@horsens.dk</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr"/>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
           <t>All weekdays in opening hours plus Saturday mornings</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="M7" s="11" t="inlineStr">
         <is>
           <t>No waiting time published; explicit process for couples abroad</t>
         </is>
       </c>
-      <c r="J7" s="13" t="inlineStr">
+      <c r="N7" s="13" t="inlineStr">
         <is>
           <t>Possible</t>
         </is>
       </c>
-      <c r="K7" s="11" t="inlineStr">
+      <c r="O7" s="11" t="inlineStr">
         <is>
           <t>Fly London (STN/LTN/LGW) to Billund BLL, approx 1h45. Car approx 40 min. Fly London STN to Aarhus AAR (Ryanair) approx 1h45, or Billund BLL.</t>
         </is>
       </c>
-      <c r="L7" s="14" t="inlineStr">
+      <c r="P7" s="14" t="inlineStr">
         <is>
           <t>https://horsens.dk</t>
         </is>
       </c>
-      <c r="M7" s="14" t="inlineStr">
+      <c r="Q7" s="14" t="inlineStr">
         <is>
           <t>https://horsens.dk/familie/livsfaser/vielse</t>
         </is>
       </c>
-      <c r="N7" s="11" t="inlineStr">
+      <c r="R7" s="11" t="inlineStr">
         <is>
           <t>Email sent, follow-up sent.</t>
         </is>
@@ -1351,35 +1501,51 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
+          <t>+45 87 94 74 67</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>skanderborg.kommune@skanderborg.dk</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K8" s="11" t="inlineStr"/>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
           <t>Mon-Tue 9-15, Wed 9-14:30, Thu 9-16:30, Sat 9-11:30</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="M8" s="11" t="inlineStr">
         <is>
           <t>No waiting time published</t>
         </is>
       </c>
-      <c r="J8" s="13" t="inlineStr">
+      <c r="N8" s="13" t="inlineStr">
         <is>
           <t>Possible</t>
         </is>
       </c>
-      <c r="K8" s="11" t="inlineStr">
+      <c r="O8" s="11" t="inlineStr">
         <is>
           <t>Fly London (STN/LTN/LGW) to Billund BLL, approx 1h45. Car approx 50 min. Fly London STN to Aarhus AAR (Ryanair) approx 1h45, or Billund BLL.</t>
         </is>
       </c>
-      <c r="L8" s="14" t="inlineStr">
+      <c r="P8" s="14" t="inlineStr">
         <is>
           <t>https://www.skanderborg.dk</t>
         </is>
       </c>
-      <c r="M8" s="14" t="inlineStr">
+      <c r="Q8" s="14" t="inlineStr">
         <is>
           <t>https://www.skanderborg.dk/borger/personlige-forhold/skal-du-giftes</t>
         </is>
       </c>
-      <c r="N8" s="11" t="inlineStr">
+      <c r="R8" s="11" t="inlineStr">
         <is>
           <t>Email sent, follow-up sent.</t>
         </is>
@@ -1417,31 +1583,47 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
+          <t>+45 54 67 67 67</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>borgerservice@lolland.dk</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="inlineStr"/>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
           <t>Most Tuesdays and Thursdays; other days on demand</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Certificates issued same day in EN/DE/DA; documents checked the day of the ceremony; established wedding-tourism town hall</t>
         </is>
       </c>
-      <c r="J9" s="13" t="inlineStr">
+      <c r="N9" s="13" t="inlineStr">
         <is>
           <t>Possible</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr">
+      <c r="O9" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to Maribo approx 2h, or car 1h45.</t>
         </is>
       </c>
-      <c r="L9" s="14" t="inlineStr">
+      <c r="P9" s="14" t="inlineStr">
         <is>
           <t>https://www.lolland.dk</t>
         </is>
       </c>
-      <c r="M9" s="11" t="inlineStr"/>
-      <c r="N9" s="11" t="inlineStr">
+      <c r="Q9" s="11" t="inlineStr"/>
+      <c r="R9" s="11" t="inlineStr">
         <is>
           <t>Strongest lead on Zealand side. Email sent, follow-up sent.</t>
         </is>
@@ -1479,31 +1661,47 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
+          <t>+45 79 94 68 00</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>vardekommune@varde.dk</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K10" s="11" t="inlineStr"/>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
           <t>Weekdays plus Saturday morning; free</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>No waiting time published; page says no address needed</t>
         </is>
       </c>
-      <c r="J10" s="13" t="inlineStr">
+      <c r="N10" s="13" t="inlineStr">
         <is>
           <t>Possible</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Fly London (STN/LTN/LGW) to Billund BLL, approx 1h45. Car approx 40 min.</t>
         </is>
       </c>
-      <c r="L10" s="14" t="inlineStr">
+      <c r="P10" s="14" t="inlineStr">
         <is>
           <t>https://www.vardekommune.dk</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr"/>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="Q10" s="11" t="inlineStr"/>
+      <c r="R10" s="11" t="inlineStr">
         <is>
           <t>Email sent, follow-up sent.</t>
         </is>
@@ -1541,35 +1739,51 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
+          <t>+45 79 96 67 93</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>post@vejen.dk</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr"/>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
           <t>All weekdays in office hours; Sat by arrangement</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="M11" s="11" t="inlineStr">
         <is>
           <t>No waiting time published</t>
         </is>
       </c>
-      <c r="J11" s="13" t="inlineStr">
+      <c r="N11" s="13" t="inlineStr">
         <is>
           <t>Possible</t>
         </is>
       </c>
-      <c r="K11" s="11" t="inlineStr">
+      <c r="O11" s="11" t="inlineStr">
         <is>
           <t>Fly London (STN/LTN/LGW) to Billund BLL, approx 1h45. Car approx 30 min.</t>
         </is>
       </c>
-      <c r="L11" s="14" t="inlineStr">
+      <c r="P11" s="14" t="inlineStr">
         <is>
           <t>https://vejen.dk</t>
         </is>
       </c>
-      <c r="M11" s="14" t="inlineStr">
+      <c r="Q11" s="14" t="inlineStr">
         <is>
           <t>https://vejen.dk/borger/familie-boern-og-unge/vielse</t>
         </is>
       </c>
-      <c r="N11" s="11" t="inlineStr">
+      <c r="R11" s="11" t="inlineStr">
         <is>
           <t>Page explicitly invites out-of-town couples. Email sent, follow-up sent.</t>
         </is>
@@ -1607,31 +1821,51 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
+          <t>48 10 01 00</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>kommunen@alleroed.dk</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>Rådhuset, Forvaltningen Bjarkesvej 2, 3450 Allerød</t>
+        </is>
+      </c>
+      <c r="K12" s="14" t="inlineStr">
+        <is>
+          <t>https://alleroed.dk/kommunen/kontakt-og-organisering/kontakt-os</t>
+        </is>
+      </c>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
           <t>not found (dedicated wedding inbox exists)</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="M12" s="11" t="inlineStr">
         <is>
           <t>No waiting time published</t>
         </is>
       </c>
-      <c r="J12" s="15" t="inlineStr">
+      <c r="N12" s="15" t="inlineStr">
         <is>
           <t>Possible (low confidence)</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr">
+      <c r="O12" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to Allerød approx 45 min.</t>
         </is>
       </c>
-      <c r="L12" s="14" t="inlineStr">
+      <c r="P12" s="14" t="inlineStr">
         <is>
           <t>https://www.alleroed.dk</t>
         </is>
       </c>
-      <c r="M12" s="11" t="inlineStr"/>
-      <c r="N12" s="11" t="inlineStr">
+      <c r="Q12" s="11" t="inlineStr"/>
+      <c r="R12" s="11" t="inlineStr">
         <is>
           <t>Sweep found the wedding mailbox but no schedule. Ask directly.</t>
         </is>
@@ -1669,31 +1903,51 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
+          <t>+45 72 56 50 00</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>fredensborg@fredensborg.dk</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>Rådhuset, Egevangen 3B, 2980 Kokkedal</t>
+        </is>
+      </c>
+      <c r="K13" s="14" t="inlineStr">
+        <is>
+          <t>https://fredensborg.dk/kommunen/kontakt-os</t>
+        </is>
+      </c>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
           <t>not found; ceremonies at Fredensborg Rådhus, Egevangen 3B, Kokkedal</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="M13" s="11" t="inlineStr">
         <is>
           <t>Own page quotes 10 days processing for a civil marriage</t>
         </is>
       </c>
-      <c r="J13" s="15" t="inlineStr">
+      <c r="N13" s="15" t="inlineStr">
         <is>
           <t>Possible (low confidence)</t>
         </is>
       </c>
-      <c r="K13" s="11" t="inlineStr">
+      <c r="O13" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to Kokkedal approx 35 min.</t>
         </is>
       </c>
-      <c r="L13" s="14" t="inlineStr">
+      <c r="P13" s="14" t="inlineStr">
         <is>
           <t>https://www.fredensborg.dk</t>
         </is>
       </c>
-      <c r="M13" s="11" t="inlineStr"/>
-      <c r="N13" s="11" t="inlineStr">
+      <c r="Q13" s="11" t="inlineStr"/>
+      <c r="R13" s="11" t="inlineStr">
         <is>
           <t>10-day processing could fit if you get the certificate by 25 Sep. Phone them.</t>
         </is>
@@ -1731,35 +1985,55 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
+          <t>47 35 10 00</t>
+        </is>
+      </c>
+      <c r="I14" s="11" t="inlineStr">
+        <is>
+          <t>borgerservice@frederikssund.dk</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>Torvet 2, 3600 Frederikssund</t>
+        </is>
+      </c>
+      <c r="K14" s="14" t="inlineStr">
+        <is>
+          <t>https://www.frederikssund.dk/kommunen/kontakt</t>
+        </is>
+      </c>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
           <t>Mon-Wed 10-14, Thu 10-16, Fri 10-13, selected Sat 10-12</t>
         </is>
       </c>
-      <c r="I14" s="11" t="inlineStr">
+      <c r="M14" s="11" t="inlineStr">
         <is>
           <t>No waiting time published</t>
         </is>
       </c>
-      <c r="J14" s="15" t="inlineStr">
+      <c r="N14" s="15" t="inlineStr">
         <is>
           <t>Possible (low confidence)</t>
         </is>
       </c>
-      <c r="K14" s="11" t="inlineStr">
+      <c r="O14" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. S-train to Frederikssund approx 55 min.</t>
         </is>
       </c>
-      <c r="L14" s="14" t="inlineStr">
+      <c r="P14" s="14" t="inlineStr">
         <is>
           <t>https://www.frederikssund.dk</t>
         </is>
       </c>
-      <c r="M14" s="14" t="inlineStr">
+      <c r="Q14" s="14" t="inlineStr">
         <is>
           <t>https://www.frederikssund.dk/Borger/Voksne--aeldre/Vielser</t>
         </is>
       </c>
-      <c r="N14" s="11" t="inlineStr">
+      <c r="R14" s="11" t="inlineStr">
         <is>
           <t>Free choice of municipality confirmed. Phone booking only.</t>
         </is>
@@ -1792,40 +2066,60 @@
       <c r="F15" s="11" t="inlineStr"/>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>Vielseskontoret by phone / web</t>
+          <t>Vielseskontoret by phone / web / PolitikOgJura@rudersdal.dk / 46 11 00 00</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
+          <t>46 11 00 00</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>Holte Midtpunkt 23, 1. sal, 2840 Holte (alternative: Stationsvej 36, 3460 Birkerød)</t>
+        </is>
+      </c>
+      <c r="K15" s="14" t="inlineStr">
+        <is>
+          <t>https://rudersdal.dk/om-kommunen/aabningstider-og-kontakt</t>
+        </is>
+      </c>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
           <t>Mon-Thu 10-14, Fri 10-12, Sat 9-12</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
+      <c r="M15" s="11" t="inlineStr">
         <is>
           <t>'Up to 4 weeks' refers to processing declarations; office sets the final date</t>
         </is>
       </c>
-      <c r="J15" s="15" t="inlineStr">
+      <c r="N15" s="15" t="inlineStr">
         <is>
           <t>Possible (low confidence)</t>
         </is>
       </c>
-      <c r="K15" s="11" t="inlineStr">
+      <c r="O15" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. S-train to Holte approx 30 min.</t>
         </is>
       </c>
-      <c r="L15" s="14" t="inlineStr">
+      <c r="P15" s="14" t="inlineStr">
         <is>
           <t>https://www.rudersdal.dk</t>
         </is>
       </c>
-      <c r="M15" s="14" t="inlineStr">
+      <c r="Q15" s="14" t="inlineStr">
         <is>
           <t>https://www.rudersdal.dk/borger/borgerservice-og-personlige-forhold/vielser-kirker-og-kirkegaarde/vielse</t>
         </is>
       </c>
-      <c r="N15" s="11" t="inlineStr">
+      <c r="R15" s="11" t="inlineStr">
         <is>
           <t>Explicit non-resident policy, six ceremony days a week. Ask whether a Familieretshuset certificate bypasses the 4 weeks.</t>
         </is>
@@ -1863,31 +2157,51 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
+          <t>98 45 50 00</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>post@frederikshavn.dk</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>Rådhus Allé 100, 9900 Frederikshavn</t>
+        </is>
+      </c>
+      <c r="K16" s="14" t="inlineStr">
+        <is>
+          <t>https://frederikshavn.dk/om-kommunen/kontakt/kontakt-og-aabningstider</t>
+        </is>
+      </c>
+      <c r="L16" s="11" t="inlineStr">
+        <is>
           <t>Weekdays 8-15, Sat 9-12; Skagen or Frederikshavn town hall</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr">
+      <c r="M16" s="11" t="inlineStr">
         <is>
           <t>No waiting time published</t>
         </is>
       </c>
-      <c r="J16" s="15" t="inlineStr">
+      <c r="N16" s="15" t="inlineStr">
         <is>
           <t>Possible (low confidence)</t>
         </is>
       </c>
-      <c r="K16" s="11" t="inlineStr">
+      <c r="O16" s="11" t="inlineStr">
         <is>
           <t>Fly London to Copenhagen CPH then 45 min hop to Aalborg AAL, or Billund BLL then approx 2h drive. Car approx 1h from Aalborg.</t>
         </is>
       </c>
-      <c r="L16" s="14" t="inlineStr">
+      <c r="P16" s="14" t="inlineStr">
         <is>
           <t>https://frederikshavn.dk</t>
         </is>
       </c>
-      <c r="M16" s="11" t="inlineStr"/>
-      <c r="N16" s="11" t="inlineStr">
+      <c r="Q16" s="11" t="inlineStr"/>
+      <c r="R16" s="11" t="inlineStr">
         <is>
           <t>Widest ceremony hours found in Jutland.</t>
         </is>
@@ -1925,35 +2239,55 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
+          <t>57 62 62 62</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>ringsted@ringsted.dk</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>Sct. Bendtsgade 1, 4100 Ringsted</t>
+        </is>
+      </c>
+      <c r="K17" s="14" t="inlineStr">
+        <is>
+          <t>https://ringsted.dk/kommunen/organisation/organisation-administrativ</t>
+        </is>
+      </c>
+      <c r="L17" s="11" t="inlineStr">
+        <is>
           <t>Most weekdays in office hours plus most Saturday mornings</t>
         </is>
       </c>
-      <c r="I17" s="11" t="inlineStr">
+      <c r="M17" s="11" t="inlineStr">
         <is>
           <t>Date arranged 'as soon as papers are in order'</t>
         </is>
       </c>
-      <c r="J17" s="15" t="inlineStr">
+      <c r="N17" s="15" t="inlineStr">
         <is>
           <t>Possible (low confidence)</t>
         </is>
       </c>
-      <c r="K17" s="11" t="inlineStr">
+      <c r="O17" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to Ringsted approx 45 min.</t>
         </is>
       </c>
-      <c r="L17" s="14" t="inlineStr">
+      <c r="P17" s="14" t="inlineStr">
         <is>
           <t>https://ringsted.dk</t>
         </is>
       </c>
-      <c r="M17" s="14" t="inlineStr">
+      <c r="Q17" s="14" t="inlineStr">
         <is>
           <t>https://ringsted.dk/borger/boern-unge-familie/vielse-separation-og-skilsmisse</t>
         </is>
       </c>
-      <c r="N17" s="11" t="inlineStr">
+      <c r="R17" s="11" t="inlineStr">
         <is>
           <t>Free choice confirmed. Phone booking only.</t>
         </is>
@@ -1991,35 +2325,55 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
+          <t>55 36 36 36</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>post@vordingborg.dk</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>Valdemarsgade 43, 4760 Vordingborg</t>
+        </is>
+      </c>
+      <c r="K18" s="14" t="inlineStr">
+        <is>
+          <t>https://www.vordingborg.dk/kommunen/kontakt-os</t>
+        </is>
+      </c>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
           <t>Wed, Fri, Sat at Rådhus, Valdemarsgade 43; witnesses supplied on weekdays</t>
         </is>
       </c>
-      <c r="I18" s="11" t="inlineStr">
+      <c r="M18" s="11" t="inlineStr">
         <is>
           <t>not found; agency lists it for international couples; documents in person the day before</t>
         </is>
       </c>
-      <c r="J18" s="15" t="inlineStr">
+      <c r="N18" s="15" t="inlineStr">
         <is>
           <t>Possible (low confidence)</t>
         </is>
       </c>
-      <c r="K18" s="11" t="inlineStr">
+      <c r="O18" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to Vordingborg approx 1h20.</t>
         </is>
       </c>
-      <c r="L18" s="14" t="inlineStr">
+      <c r="P18" s="14" t="inlineStr">
         <is>
           <t>https://vordingborg.dk</t>
         </is>
       </c>
-      <c r="M18" s="14" t="inlineStr">
+      <c r="Q18" s="14" t="inlineStr">
         <is>
           <t>https://vordingborg.dk/borger/borgerservice/aegteskab/borgerlig-vielse</t>
         </is>
       </c>
-      <c r="N18" s="11" t="inlineStr">
+      <c r="R18" s="11" t="inlineStr">
         <is>
           <t>Three ceremony days a week incl. Saturday.</t>
         </is>
@@ -2057,35 +2411,55 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
+          <t>72 53 05 30</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>fmk@fmk.dk</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>Faaborg-Midtfyn Kommune, Tinghøj Allé 2, 5750 Ringe (per search summary: Borgerservice Ringe rådhus at Lindevej 5, 5750 Ringe; Borgerservice Faaborg rådhus at Mellemgade 15, 5600 Faaborg)</t>
+        </is>
+      </c>
+      <c r="K19" s="14" t="inlineStr">
+        <is>
+          <t>https://www.fmk.dk/om-kommunen/kontakt/</t>
+        </is>
+      </c>
+      <c r="L19" s="11" t="inlineStr">
+        <is>
           <t>not found; venues Ringe (Tinghøj Allé 2) or Faaborg (Mellemgade 15)</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="M19" s="11" t="inlineStr">
         <is>
           <t>Explicit procedure for non-resident couples: send certificate, date/place, witnesses' names; approx 2 weeks for own certificates; no fee</t>
         </is>
       </c>
-      <c r="J19" s="15" t="inlineStr">
+      <c r="N19" s="15" t="inlineStr">
         <is>
           <t>Possible (low confidence)</t>
         </is>
       </c>
-      <c r="K19" s="11" t="inlineStr">
+      <c r="O19" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to Odense 1h15 then local train to Ringe 25 min. Or Billund plus car 1h15.</t>
         </is>
       </c>
-      <c r="L19" s="14" t="inlineStr">
+      <c r="P19" s="14" t="inlineStr">
         <is>
           <t>https://www.fmk.dk</t>
         </is>
       </c>
-      <c r="M19" s="14" t="inlineStr">
+      <c r="Q19" s="14" t="inlineStr">
         <is>
           <t>https://www.fmk.dk/borger/borgerservice/aegteskab-og-vielse/bliv-gift-i-faaborg-midtfyn-kommune/</t>
         </is>
       </c>
-      <c r="N19" s="11" t="inlineStr">
+      <c r="R19" s="11" t="inlineStr">
         <is>
           <t>Clear out-of-town procedure.</t>
         </is>
@@ -2123,35 +2497,55 @@
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
+          <t>65 15 15 15</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>borgerservice@kerteminde.dk</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>Hans Schacksvej 4, 5300 Kerteminde</t>
+        </is>
+      </c>
+      <c r="K20" s="14" t="inlineStr">
+        <is>
+          <t>https://kerteminde.dk/kommunen/kontakt-os</t>
+        </is>
+      </c>
+      <c r="L20" s="11" t="inlineStr">
+        <is>
           <t>Mon-Thu 10-15 (not July/holidays); Sat 10-12; Rådhus Hans Schacksvej 4</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr">
+      <c r="M20" s="11" t="inlineStr">
         <is>
           <t>Municipality contacts you to fix date after documents</t>
         </is>
       </c>
-      <c r="J20" s="15" t="inlineStr">
+      <c r="N20" s="15" t="inlineStr">
         <is>
           <t>Possible (low confidence)</t>
         </is>
       </c>
-      <c r="K20" s="11" t="inlineStr">
+      <c r="O20" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to Odense 1h15 then bus 30 min.</t>
         </is>
       </c>
-      <c r="L20" s="14" t="inlineStr">
+      <c r="P20" s="14" t="inlineStr">
         <is>
           <t>https://www.kerteminde.dk</t>
         </is>
       </c>
-      <c r="M20" s="14" t="inlineStr">
+      <c r="Q20" s="14" t="inlineStr">
         <is>
           <t>https://www.kerteminde.dk/borger/borgerservice/vielse</t>
         </is>
       </c>
-      <c r="N20" s="11" t="inlineStr">
+      <c r="R20" s="11" t="inlineStr">
         <is>
           <t>Small municipality, four weekdays plus Saturday.</t>
         </is>
@@ -2189,35 +2583,55 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
+          <t>62 23 30 00</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>svendborg@svendborg.dk</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>Ramsherred 5, 5700 Svendborg</t>
+        </is>
+      </c>
+      <c r="K21" s="14" t="inlineStr">
+        <is>
+          <t>https://www.svendborg.dk/om-kommunen/kontakt-svendborg-kommune/</t>
+        </is>
+      </c>
+      <c r="L21" s="11" t="inlineStr">
+        <is>
           <t>Mon-Sat; weekdays at Rådhus, Sat 12-15 at other venues</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J21" s="15" t="inlineStr">
+      <c r="M21" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N21" s="15" t="inlineStr">
         <is>
           <t>Possible (low confidence)</t>
         </is>
       </c>
-      <c r="K21" s="11" t="inlineStr">
+      <c r="O21" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to Svendborg approx 2h.</t>
         </is>
       </c>
-      <c r="L21" s="14" t="inlineStr">
+      <c r="P21" s="14" t="inlineStr">
         <is>
           <t>https://www.svendborg.dk</t>
         </is>
       </c>
-      <c r="M21" s="14" t="inlineStr">
+      <c r="Q21" s="14" t="inlineStr">
         <is>
           <t>https://www.svendborg.dk/borger/borgerservice/vielse/vielse-paa-svendborg-raadhus/</t>
         </is>
       </c>
-      <c r="N21" s="11" t="inlineStr">
+      <c r="R21" s="11" t="inlineStr">
         <is>
           <t>Booked by phone, so you learn availability immediately.</t>
         </is>
@@ -2255,35 +2669,55 @@
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
+          <t>4323 6100</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>borgerservice@glostrup.dk</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>Rådhusparken 2, 2600 Glostrup</t>
+        </is>
+      </c>
+      <c r="K22" s="14" t="inlineStr">
+        <is>
+          <t>https://www.glostrup.dk/find</t>
+        </is>
+      </c>
+      <c r="L22" s="11" t="inlineStr">
+        <is>
           <t>Mon-Fri in opening hours plus Saturdays</t>
         </is>
       </c>
-      <c r="I22" s="11" t="inlineStr">
+      <c r="M22" s="11" t="inlineStr">
         <is>
           <t>not found; not on any agency list, so no third-party evidence</t>
         </is>
       </c>
-      <c r="J22" s="17" t="inlineStr">
+      <c r="N22" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K22" s="11" t="inlineStr">
+      <c r="O22" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. S-train to Glostrup approx 20 min.</t>
         </is>
       </c>
-      <c r="L22" s="14" t="inlineStr">
+      <c r="P22" s="14" t="inlineStr">
         <is>
           <t>https://glostrup.dk</t>
         </is>
       </c>
-      <c r="M22" s="14" t="inlineStr">
+      <c r="Q22" s="14" t="inlineStr">
         <is>
           <t>https://glostrup.dk/borger/borgerservice/vielse</t>
         </is>
       </c>
-      <c r="N22" s="11" t="inlineStr">
+      <c r="R22" s="11" t="inlineStr">
         <is>
           <t>Draft email ready in Gmail (system blocked auto-send).</t>
         </is>
@@ -2321,35 +2755,51 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
+          <t>+45 43 59 10 00</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>cba-kh-ey@htk.dk</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K23" s="11" t="inlineStr"/>
+      <c r="L23" s="11" t="inlineStr">
+        <is>
           <t>Mon-Wed 10-14:30, Thu 10-17, Fri 10-13:30 plus selected dates</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J23" s="17" t="inlineStr">
+      <c r="M23" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N23" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K23" s="11" t="inlineStr">
+      <c r="O23" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to Høje Taastrup approx 20 min.</t>
         </is>
       </c>
-      <c r="L23" s="14" t="inlineStr">
+      <c r="P23" s="14" t="inlineStr">
         <is>
           <t>https://www.htk.dk</t>
         </is>
       </c>
-      <c r="M23" s="14" t="inlineStr">
+      <c r="Q23" s="14" t="inlineStr">
         <is>
           <t>https://www.htk.dk/borger/borgerservice/vielse-og-skilsmisse</t>
         </is>
       </c>
-      <c r="N23" s="11" t="inlineStr">
+      <c r="R23" s="11" t="inlineStr">
         <is>
           <t>Daily weekday ceremonies; non-resident policy unconfirmed.</t>
         </is>
@@ -2387,35 +2837,55 @@
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
+          <t>32 47 11 11</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>kommunen@taarnby.dk</t>
+        </is>
+      </c>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
+          <t>Amager Landevej 76, 2770 Kastrup</t>
+        </is>
+      </c>
+      <c r="K24" s="14" t="inlineStr">
+        <is>
+          <t>https://www.taarnby.dk/om-kommunen/kontakt/kontakt-os/</t>
+        </is>
+      </c>
+      <c r="L24" s="11" t="inlineStr">
+        <is>
           <t>Fridays 11:00; 3rd Saturday of month 10:00</t>
         </is>
       </c>
-      <c r="I24" s="11" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J24" s="17" t="inlineStr">
+      <c r="M24" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N24" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K24" s="11" t="inlineStr">
+      <c r="O24" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Metro one stop from airport, approx 10 min.</t>
         </is>
       </c>
-      <c r="L24" s="14" t="inlineStr">
+      <c r="P24" s="14" t="inlineStr">
         <is>
           <t>https://taarnby.dk</t>
         </is>
       </c>
-      <c r="M24" s="14" t="inlineStr">
+      <c r="Q24" s="14" t="inlineStr">
         <is>
           <t>https://taarnby.dk/borger/personlige-forhold/sadan-bliver-i-gift/</t>
         </is>
       </c>
-      <c r="N24" s="11" t="inlineStr">
+      <c r="R24" s="11" t="inlineStr">
         <is>
           <t>Only Fri 2 Oct falls in the window.</t>
         </is>
@@ -2453,35 +2923,55 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
+          <t>89 64 10 10</t>
+        </is>
+      </c>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>favrskov@favrskov.dk</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>Skovvej 20, 8382 Hinnerup</t>
+        </is>
+      </c>
+      <c r="K25" s="14" t="inlineStr">
+        <is>
+          <t>https://favrskov.dk/en/node/188</t>
+        </is>
+      </c>
+      <c r="L25" s="11" t="inlineStr">
+        <is>
           <t>Mon, Tue, Thu, Fri office hours; Sat 10-12</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr">
+      <c r="M25" s="11" t="inlineStr">
         <is>
           <t>Approx 2 weeks (declaration processing)</t>
         </is>
       </c>
-      <c r="J25" s="17" t="inlineStr">
+      <c r="N25" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K25" s="11" t="inlineStr">
+      <c r="O25" s="11" t="inlineStr">
         <is>
           <t>Fly London STN to Aarhus AAR (Ryanair) approx 1h45, or Billund BLL. Car approx 30 min from Aarhus airport.</t>
         </is>
       </c>
-      <c r="L25" s="14" t="inlineStr">
+      <c r="P25" s="14" t="inlineStr">
         <is>
           <t>https://favrskov.dk</t>
         </is>
       </c>
-      <c r="M25" s="14" t="inlineStr">
+      <c r="Q25" s="14" t="inlineStr">
         <is>
           <t>https://favrskov.dk/en/node/81</t>
         </is>
       </c>
-      <c r="N25" s="11" t="inlineStr"/>
+      <c r="R25" s="11" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="n">
@@ -2515,31 +3005,51 @@
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>79 75 50 00</t>
         </is>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J26" s="17" t="inlineStr">
+          <t>borgerservice@hedensted.dk</t>
+        </is>
+      </c>
+      <c r="J26" s="11" t="inlineStr">
+        <is>
+          <t>Niels Espes Vej 8, 8722 Hedensted</t>
+        </is>
+      </c>
+      <c r="K26" s="14" t="inlineStr">
+        <is>
+          <t>https://www.hedensted.dk/om-kommunen/kontakt/kontakt-og-aabningstider</t>
+        </is>
+      </c>
+      <c r="L26" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M26" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N26" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K26" s="11" t="inlineStr">
+      <c r="O26" s="11" t="inlineStr">
         <is>
           <t>Fly London (STN/LTN/LGW) to Billund BLL, approx 1h45. Car approx 40 min.</t>
         </is>
       </c>
-      <c r="L26" s="14" t="inlineStr">
+      <c r="P26" s="14" t="inlineStr">
         <is>
           <t>https://www.hedensted.dk</t>
         </is>
       </c>
-      <c r="M26" s="11" t="inlineStr"/>
-      <c r="N26" s="11" t="inlineStr"/>
+      <c r="Q26" s="11" t="inlineStr"/>
+      <c r="R26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="n">
@@ -2573,31 +3083,47 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
+          <t>+45 96 28 24 00</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>bos-vielser@herning.dk</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K27" s="11" t="inlineStr"/>
+      <c r="L27" s="11" t="inlineStr">
+        <is>
           <t>Thursdays and Saturdays</t>
         </is>
       </c>
-      <c r="I27" s="11" t="inlineStr">
+      <c r="M27" s="11" t="inlineStr">
         <is>
           <t>No waiting time published</t>
         </is>
       </c>
-      <c r="J27" s="17" t="inlineStr">
+      <c r="N27" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K27" s="11" t="inlineStr">
+      <c r="O27" s="11" t="inlineStr">
         <is>
           <t>Fly London (STN/LTN/LGW) to Billund BLL, approx 1h45. Car approx 50 min.</t>
         </is>
       </c>
-      <c r="L27" s="14" t="inlineStr">
+      <c r="P27" s="14" t="inlineStr">
         <is>
           <t>https://www.herning.dk</t>
         </is>
       </c>
-      <c r="M27" s="11" t="inlineStr"/>
-      <c r="N27" s="11" t="inlineStr">
+      <c r="Q27" s="11" t="inlineStr"/>
+      <c r="R27" s="11" t="inlineStr">
         <is>
           <t>Only Thu 1 Oct and Sat 3 Oct in window.</t>
         </is>
@@ -2635,31 +3161,51 @@
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
+          <t>89 59 10 00</t>
+        </is>
+      </c>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>norddjurs@norddjurs.dk</t>
+        </is>
+      </c>
+      <c r="J28" s="11" t="inlineStr">
+        <is>
+          <t>Torvet 3, 8500 Grenaa</t>
+        </is>
+      </c>
+      <c r="K28" s="14" t="inlineStr">
+        <is>
+          <t>https://norddjurs.dk/kontakt</t>
+        </is>
+      </c>
+      <c r="L28" s="11" t="inlineStr">
+        <is>
           <t>By appointment at Grenaa town hall</t>
         </is>
       </c>
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J28" s="17" t="inlineStr">
+      <c r="M28" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N28" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K28" s="11" t="inlineStr">
+      <c r="O28" s="11" t="inlineStr">
         <is>
           <t>Fly London STN to Aarhus AAR (Ryanair) approx 1h45, or Billund BLL. Car approx 35 min from Aarhus airport.</t>
         </is>
       </c>
-      <c r="L28" s="14" t="inlineStr">
+      <c r="P28" s="14" t="inlineStr">
         <is>
           <t>https://www.norddjurs.dk</t>
         </is>
       </c>
-      <c r="M28" s="11" t="inlineStr"/>
-      <c r="N28" s="11" t="inlineStr"/>
+      <c r="Q28" s="11" t="inlineStr"/>
+      <c r="R28" s="11" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="n">
@@ -2688,40 +3234,60 @@
       <c r="F29" s="11" t="inlineStr"/>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>+45 89 15 15 15</t>
+          <t>+45 89 15 15 15 / Borgerservice: phone 89 15 15 15, email borgerservice@randers.dk (Saturday cancellations: 89 15 16 50)</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
+          <t>89151600</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>borger@randers.dk</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>Rådhuset, Laksetorvet 1, 8900 Randers C</t>
+        </is>
+      </c>
+      <c r="K29" s="14" t="inlineStr">
+        <is>
+          <t>https://www.randers.dk/kontakt/</t>
+        </is>
+      </c>
+      <c r="L29" s="11" t="inlineStr">
+        <is>
           <t>Fri and Sat from 10:00, 15-min slots</t>
         </is>
       </c>
-      <c r="I29" s="11" t="inlineStr">
+      <c r="M29" s="11" t="inlineStr">
         <is>
           <t>No waiting time published</t>
         </is>
       </c>
-      <c r="J29" s="17" t="inlineStr">
+      <c r="N29" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K29" s="11" t="inlineStr">
+      <c r="O29" s="11" t="inlineStr">
         <is>
           <t>Fly London STN to Aarhus AAR (Ryanair) approx 1h45, or Billund BLL. Car approx 40 min. Or Aalborg.</t>
         </is>
       </c>
-      <c r="L29" s="14" t="inlineStr">
+      <c r="P29" s="14" t="inlineStr">
         <is>
           <t>https://www.randers.dk</t>
         </is>
       </c>
-      <c r="M29" s="14" t="inlineStr">
+      <c r="Q29" s="14" t="inlineStr">
         <is>
           <t>https://www.randers.dk/borger/personligt/aegteskab-og-parforhold/vielse-paa-raadhuset/</t>
         </is>
       </c>
-      <c r="N29" s="11" t="inlineStr">
+      <c r="R29" s="11" t="inlineStr">
         <is>
           <t>Explicitly takes couples abroad by phone. Only Fri 2, Sat 3 Oct in window.</t>
         </is>
@@ -2759,31 +3325,51 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>89 70 10 00</t>
         </is>
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J30" s="17" t="inlineStr">
+          <t>borgerservice@silkeborg.dk</t>
+        </is>
+      </c>
+      <c r="J30" s="11" t="inlineStr">
+        <is>
+          <t>Rådhuset Søvej 1, 8600 Silkeborg</t>
+        </is>
+      </c>
+      <c r="K30" s="14" t="inlineStr">
+        <is>
+          <t>https://silkeborg.dk/kommunen/kontakt-og-aabningstider</t>
+        </is>
+      </c>
+      <c r="L30" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M30" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N30" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K30" s="11" t="inlineStr">
+      <c r="O30" s="11" t="inlineStr">
         <is>
           <t>Fly London (STN/LTN/LGW) to Billund BLL, approx 1h45. Car approx 1h. Or Aarhus airport 1h.</t>
         </is>
       </c>
-      <c r="L30" s="14" t="inlineStr">
+      <c r="P30" s="14" t="inlineStr">
         <is>
           <t>https://silkeborg.dk</t>
         </is>
       </c>
-      <c r="M30" s="11" t="inlineStr"/>
-      <c r="N30" s="11" t="inlineStr"/>
+      <c r="Q30" s="11" t="inlineStr"/>
+      <c r="R30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="n">
@@ -2817,31 +3403,51 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>87 53 50 00</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J31" s="17" t="inlineStr">
+          <t>syddjurs@syddjurs.dk</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K31" s="14" t="inlineStr">
+        <is>
+          <t>https://www.syddjurs.dk/om-kommunen/kontakt</t>
+        </is>
+      </c>
+      <c r="L31" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M31" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N31" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K31" s="11" t="inlineStr">
+      <c r="O31" s="11" t="inlineStr">
         <is>
           <t>Fly London STN to Aarhus AAR (Ryanair) approx 1h45, or Billund BLL. Aarhus airport is inside Syddjurs; 15 min to Rønde.</t>
         </is>
       </c>
-      <c r="L31" s="14" t="inlineStr">
+      <c r="P31" s="14" t="inlineStr">
         <is>
           <t>https://www.syddjurs.dk</t>
         </is>
       </c>
-      <c r="M31" s="11" t="inlineStr"/>
-      <c r="N31" s="11" t="inlineStr">
+      <c r="Q31" s="11" t="inlineStr"/>
+      <c r="R31" s="11" t="inlineStr">
         <is>
           <t>Closest town hall to Aarhus airport.</t>
         </is>
@@ -2879,31 +3485,51 @@
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
+          <t>87 87 87 87</t>
+        </is>
+      </c>
+      <c r="I32" s="11" t="inlineStr">
+        <is>
+          <t>sikkerborgerservice@viborg.dk</t>
+        </is>
+      </c>
+      <c r="J32" s="11" t="inlineStr">
+        <is>
+          <t>Prinsens Alle 5, 8800 Viborg</t>
+        </is>
+      </c>
+      <c r="K32" s="14" t="inlineStr">
+        <is>
+          <t>https://viborg.dk/om-kommunen/kontakt-og-aabningstider/</t>
+        </is>
+      </c>
+      <c r="L32" s="11" t="inlineStr">
+        <is>
           <t>Most Thu, Fri, Sat; 4 per day</t>
         </is>
       </c>
-      <c r="I32" s="11" t="inlineStr">
+      <c r="M32" s="11" t="inlineStr">
         <is>
           <t>Most Saturdays taken</t>
         </is>
       </c>
-      <c r="J32" s="17" t="inlineStr">
+      <c r="N32" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K32" s="11" t="inlineStr">
+      <c r="O32" s="11" t="inlineStr">
         <is>
           <t>Fly London (STN/LTN/LGW) to Billund BLL, approx 1h45. Car approx 1h15. Or Aarhus airport 1h.</t>
         </is>
       </c>
-      <c r="L32" s="14" t="inlineStr">
+      <c r="P32" s="14" t="inlineStr">
         <is>
           <t>https://viborg.dk</t>
         </is>
       </c>
-      <c r="M32" s="11" t="inlineStr"/>
-      <c r="N32" s="11" t="inlineStr"/>
+      <c r="Q32" s="11" t="inlineStr"/>
+      <c r="R32" s="11" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="n">
@@ -2937,31 +3563,51 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>9945 4545</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J33" s="17" t="inlineStr">
+          <t>raadhus@99454545.dk</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>Ny Rådhusplads 1, 9700 Brønderslev</t>
+        </is>
+      </c>
+      <c r="K33" s="14" t="inlineStr">
+        <is>
+          <t>https://www.bronderslev.dk/om-kommunen/kontakt-borgerservice</t>
+        </is>
+      </c>
+      <c r="L33" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M33" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N33" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K33" s="11" t="inlineStr">
+      <c r="O33" s="11" t="inlineStr">
         <is>
           <t>Fly London to Copenhagen CPH then 45 min hop to Aalborg AAL, or Billund BLL then approx 2h drive. Car 30 min from Aalborg.</t>
         </is>
       </c>
-      <c r="L33" s="14" t="inlineStr">
+      <c r="P33" s="14" t="inlineStr">
         <is>
           <t>https://www.bronderslev.dk</t>
         </is>
       </c>
-      <c r="M33" s="11" t="inlineStr"/>
-      <c r="N33" s="11" t="inlineStr"/>
+      <c r="Q33" s="11" t="inlineStr"/>
+      <c r="R33" s="11" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="n">
@@ -2995,31 +3641,51 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>97 11 30 00</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J34" s="17" t="inlineStr">
+          <t>raadhus@mariagerfjord.dk</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>Nordre Kajgade 1, 9500 Hobro</t>
+        </is>
+      </c>
+      <c r="K34" s="14" t="inlineStr">
+        <is>
+          <t>https://www.mariagerfjord.dk/om-os/kontakt</t>
+        </is>
+      </c>
+      <c r="L34" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M34" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N34" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K34" s="11" t="inlineStr">
+      <c r="O34" s="11" t="inlineStr">
         <is>
           <t>Fly London to Copenhagen CPH then 45 min hop to Aalborg AAL, or Billund BLL then approx 2h drive. Car 40 min from Aalborg.</t>
         </is>
       </c>
-      <c r="L34" s="14" t="inlineStr">
+      <c r="P34" s="14" t="inlineStr">
         <is>
           <t>https://www.mariagerfjord.dk</t>
         </is>
       </c>
-      <c r="M34" s="11" t="inlineStr"/>
-      <c r="N34" s="11" t="inlineStr"/>
+      <c r="Q34" s="11" t="inlineStr"/>
+      <c r="R34" s="11" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="n">
@@ -3053,31 +3719,51 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
+          <t>99 88 99 88</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>raadhus@rebild.dk</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>Hobrovej 110, 9530 Støvring</t>
+        </is>
+      </c>
+      <c r="K35" s="14" t="inlineStr">
+        <is>
+          <t>https://rebild.dk/om-kommunen/kontakt</t>
+        </is>
+      </c>
+      <c r="L35" s="11" t="inlineStr">
+        <is>
           <t>English ceremonies in office hours</t>
         </is>
       </c>
-      <c r="I35" s="11" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J35" s="17" t="inlineStr">
+      <c r="M35" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N35" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K35" s="11" t="inlineStr">
+      <c r="O35" s="11" t="inlineStr">
         <is>
           <t>Fly London to Copenhagen CPH then 45 min hop to Aalborg AAL, or Billund BLL then approx 2h drive. Car 25 min from Aalborg.</t>
         </is>
       </c>
-      <c r="L35" s="14" t="inlineStr">
+      <c r="P35" s="14" t="inlineStr">
         <is>
           <t>https://rebild.dk</t>
         </is>
       </c>
-      <c r="M35" s="11" t="inlineStr"/>
-      <c r="N35" s="11" t="inlineStr"/>
+      <c r="Q35" s="11" t="inlineStr"/>
+      <c r="R35" s="11" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="n">
@@ -3111,35 +3797,55 @@
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
+          <t>56 20 30 00</t>
+        </is>
+      </c>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>kommunen@faxekommune.dk</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>Frederiksgade 9, 4690 Haslev (also Rådhusvej 4, 4640 Fakse)</t>
+        </is>
+      </c>
+      <c r="K36" s="14" t="inlineStr">
+        <is>
+          <t>https://www.faxekommune.dk/da/kontakt-aabningstider</t>
+        </is>
+      </c>
+      <c r="L36" s="11" t="inlineStr">
+        <is>
           <t>Mon-Sat, council chamber</t>
         </is>
       </c>
-      <c r="I36" s="11" t="inlineStr">
+      <c r="M36" s="11" t="inlineStr">
         <is>
           <t>Apply up to 4 months ahead; closed July and holidays</t>
         </is>
       </c>
-      <c r="J36" s="17" t="inlineStr">
+      <c r="N36" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K36" s="11" t="inlineStr">
+      <c r="O36" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to Haslev approx 55 min.</t>
         </is>
       </c>
-      <c r="L36" s="14" t="inlineStr">
+      <c r="P36" s="14" t="inlineStr">
         <is>
           <t>https://www.faxekommune.dk</t>
         </is>
       </c>
-      <c r="M36" s="14" t="inlineStr">
+      <c r="Q36" s="14" t="inlineStr">
         <is>
           <t>https://www.faxekommune.dk/da/borger/borgerservice/aegteskab-parforhold/ansoeg-om-vielse</t>
         </is>
       </c>
-      <c r="N36" s="11" t="inlineStr">
+      <c r="R36" s="11" t="inlineStr">
         <is>
           <t>Free choice confirmed; six ceremony days a week.</t>
         </is>
@@ -3177,35 +3883,55 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
+          <t>+45 43 97 97 97</t>
+        </is>
+      </c>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>raadhus@greve.dk</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>Greve Rådhus, Rådhusholmen 10, 2670 Greve</t>
+        </is>
+      </c>
+      <c r="K37" s="14" t="inlineStr">
+        <is>
+          <t>https://greve.dk/kommunen/kontakt</t>
+        </is>
+      </c>
+      <c r="L37" s="11" t="inlineStr">
+        <is>
           <t>Booking Mon-Thu; Fri closed</t>
         </is>
       </c>
-      <c r="I37" s="11" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J37" s="17" t="inlineStr">
+      <c r="M37" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N37" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K37" s="11" t="inlineStr">
+      <c r="O37" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. S-train to Greve approx 35 min.</t>
         </is>
       </c>
-      <c r="L37" s="14" t="inlineStr">
+      <c r="P37" s="14" t="inlineStr">
         <is>
           <t>https://www.greve.dk</t>
         </is>
       </c>
-      <c r="M37" s="14" t="inlineStr">
+      <c r="Q37" s="14" t="inlineStr">
         <is>
           <t>https://www.greve.dk/voksne-og-aeldre/selvbetjening/vielse</t>
         </is>
       </c>
-      <c r="N37" s="11" t="inlineStr"/>
+      <c r="R37" s="11" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="n">
@@ -3239,35 +3965,55 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
+          <t>54 73 10 00</t>
+        </is>
+      </c>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>ga@guldborgsund.dk</t>
+        </is>
+      </c>
+      <c r="J38" s="11" t="inlineStr">
+        <is>
+          <t>Parkvej 37, 4800 Nykøbing F.</t>
+        </is>
+      </c>
+      <c r="K38" s="14" t="inlineStr">
+        <is>
+          <t>https://www.guldborgsund.dk/</t>
+        </is>
+      </c>
+      <c r="L38" s="11" t="inlineStr">
+        <is>
           <t>Weekdays usually 10-12 (witnesses provided); Saturdays outside town hall</t>
         </is>
       </c>
-      <c r="I38" s="11" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J38" s="17" t="inlineStr">
+      <c r="M38" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N38" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K38" s="11" t="inlineStr">
+      <c r="O38" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to Nykøbing F approx 1h30.</t>
         </is>
       </c>
-      <c r="L38" s="14" t="inlineStr">
+      <c r="P38" s="14" t="inlineStr">
         <is>
           <t>https://www.guldborgsund.dk</t>
         </is>
       </c>
-      <c r="M38" s="14" t="inlineStr">
+      <c r="Q38" s="14" t="inlineStr">
         <is>
           <t>https://www.guldborgsund.dk/borger/borgerservice/vielse-og-aegteskab</t>
         </is>
       </c>
-      <c r="N38" s="11" t="inlineStr">
+      <c r="R38" s="11" t="inlineStr">
         <is>
           <t>Accepts Familieretshuset certificates.</t>
         </is>
@@ -3300,40 +4046,60 @@
       <c r="F39" s="11" t="inlineStr"/>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>Web / phone</t>
+          <t>Web / phone / Kultur- og Fritidssekretariatet, phone 72 36 36 36 (Mon-Fri 8:00-13:00); no wedding email found</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
+          <t>72 36 36 36</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>Jernbanevej 6, 4300 Holbæk</t>
+        </is>
+      </c>
+      <c r="K39" s="14" t="inlineStr">
+        <is>
+          <t>https://holbaek.dk/kontakt</t>
+        </is>
+      </c>
+      <c r="L39" s="11" t="inlineStr">
+        <is>
           <t>Approx 5 ceremonies a week</t>
         </is>
       </c>
-      <c r="I39" s="11" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J39" s="17" t="inlineStr">
+      <c r="M39" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N39" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K39" s="11" t="inlineStr">
+      <c r="O39" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to Holbæk approx 1h.</t>
         </is>
       </c>
-      <c r="L39" s="14" t="inlineStr">
+      <c r="P39" s="14" t="inlineStr">
         <is>
           <t>https://holbaek.dk</t>
         </is>
       </c>
-      <c r="M39" s="14" t="inlineStr">
+      <c r="Q39" s="14" t="inlineStr">
         <is>
           <t>https://holbaek.dk/service-og-selvbetjening/personlige-forhold/aegteskab-og-skilsmisse/naar-i-vil-giftes</t>
         </is>
       </c>
-      <c r="N39" s="11" t="inlineStr">
+      <c r="R39" s="11" t="inlineStr">
         <is>
           <t>Explicitly marries non-residents.</t>
         </is>
@@ -3371,35 +4137,55 @@
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
+          <t>56 57 57 57</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>stevns@stevns.dk</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="inlineStr">
+        <is>
+          <t>Rådhuspladsen 4, 4660 Store Heddinge</t>
+        </is>
+      </c>
+      <c r="K40" s="14" t="inlineStr">
+        <is>
+          <t>https://www.stevns.dk/kontakt</t>
+        </is>
+      </c>
+      <c r="L40" s="11" t="inlineStr">
+        <is>
           <t>not found; office closed 12-17 Oct</t>
         </is>
       </c>
-      <c r="I40" s="11" t="inlineStr">
+      <c r="M40" s="11" t="inlineStr">
         <is>
           <t>Site says earliest available appointment 'October 2026'</t>
         </is>
       </c>
-      <c r="J40" s="17" t="inlineStr">
+      <c r="N40" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K40" s="11" t="inlineStr">
+      <c r="O40" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to Køge then local train approx 1h10.</t>
         </is>
       </c>
-      <c r="L40" s="14" t="inlineStr">
+      <c r="P40" s="14" t="inlineStr">
         <is>
           <t>https://stevns.dk</t>
         </is>
       </c>
-      <c r="M40" s="14" t="inlineStr">
+      <c r="Q40" s="14" t="inlineStr">
         <is>
           <t>https://stevns.dk/service-and-selvbetjening/borgerservice/bliv-gift</t>
         </is>
       </c>
-      <c r="N40" s="11" t="inlineStr">
+      <c r="R40" s="11" t="inlineStr">
         <is>
           <t>Listed by Marry Abroad Simply as a venue. 'October 2026' may include your window: phone them.</t>
         </is>
@@ -3437,35 +4223,55 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>64 74 74 74</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J41" s="17" t="inlineStr">
+          <t>assens@assens.dk</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr">
+        <is>
+          <t>Rådhus Allé 5, 5610 Assens</t>
+        </is>
+      </c>
+      <c r="K41" s="14" t="inlineStr">
+        <is>
+          <t>https://www.assens.dk/om-os/kontakt-os</t>
+        </is>
+      </c>
+      <c r="L41" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M41" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N41" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K41" s="11" t="inlineStr">
+      <c r="O41" s="11" t="inlineStr">
         <is>
           <t>Fly London (STN/LTN/LGW) to Billund BLL, approx 1h45. Car approx 1h. Or CPH plus train to Odense 1h15 then bus 45 min.</t>
         </is>
       </c>
-      <c r="L41" s="14" t="inlineStr">
+      <c r="P41" s="14" t="inlineStr">
         <is>
           <t>https://www.assens.dk</t>
         </is>
       </c>
-      <c r="M41" s="14" t="inlineStr">
+      <c r="Q41" s="14" t="inlineStr">
         <is>
           <t>https://www.assens.dk/borger/personlige-forhold/vielse</t>
         </is>
       </c>
-      <c r="N41" s="11" t="inlineStr">
+      <c r="R41" s="11" t="inlineStr">
         <is>
           <t>Not restricted; routes foreigners via Familieretshuset.</t>
         </is>
@@ -3503,31 +4309,51 @@
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
+          <t>79 72 72 00</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="inlineStr">
+        <is>
+          <t>kommunen@billund.dk</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
+          <t>Jorden Rundt 1, 7200 Grindsted</t>
+        </is>
+      </c>
+      <c r="K42" s="14" t="inlineStr">
+        <is>
+          <t>https://www.billund.dk/om-kommunen/kontakt-os/</t>
+        </is>
+      </c>
+      <c r="L42" s="11" t="inlineStr">
+        <is>
           <t>not found; council chamber Grindsted</t>
         </is>
       </c>
-      <c r="I42" s="11" t="inlineStr">
+      <c r="M42" s="11" t="inlineStr">
         <is>
           <t>State wished dates in the declaration; they call back</t>
         </is>
       </c>
-      <c r="J42" s="17" t="inlineStr">
+      <c r="N42" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K42" s="11" t="inlineStr">
+      <c r="O42" s="11" t="inlineStr">
         <is>
           <t>Fly London (STN/LTN/LGW) to Billund BLL, approx 1h45. Town hall in Grindsted approx 20 min from airport.</t>
         </is>
       </c>
-      <c r="L42" s="14" t="inlineStr">
+      <c r="P42" s="14" t="inlineStr">
         <is>
           <t>https://billund.dk</t>
         </is>
       </c>
-      <c r="M42" s="11" t="inlineStr"/>
-      <c r="N42" s="11" t="inlineStr">
+      <c r="Q42" s="11" t="inlineStr"/>
+      <c r="R42" s="11" t="inlineStr">
         <is>
           <t>Closest town hall to Billund airport.</t>
         </is>
@@ -3565,31 +4391,51 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
+          <t>7210 7000</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>kommunen@fredericia.dk</t>
+        </is>
+      </c>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>Rådhuset, Gothersgade 20, 7000 Fredericia</t>
+        </is>
+      </c>
+      <c r="K43" s="14" t="inlineStr">
+        <is>
+          <t>https://www.fredericia.dk/da/om-kommunen/kontakt</t>
+        </is>
+      </c>
+      <c r="L43" s="11" t="inlineStr">
+        <is>
           <t>Weekdays in council chamber; most Saturdays 10-11</t>
         </is>
       </c>
-      <c r="I43" s="11" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J43" s="17" t="inlineStr">
+      <c r="M43" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N43" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K43" s="11" t="inlineStr">
+      <c r="O43" s="11" t="inlineStr">
         <is>
           <t>Fly London (STN/LTN/LGW) to Billund BLL, approx 1h45. Car approx 45 min. Or CPH plus train 2h.</t>
         </is>
       </c>
-      <c r="L43" s="14" t="inlineStr">
+      <c r="P43" s="14" t="inlineStr">
         <is>
           <t>https://www.fredericia.dk</t>
         </is>
       </c>
-      <c r="M43" s="11" t="inlineStr"/>
-      <c r="N43" s="11" t="inlineStr">
+      <c r="Q43" s="11" t="inlineStr"/>
+      <c r="R43" s="11" t="inlineStr">
         <is>
           <t>Routes foreigners via Familieretshuset; no residency bar found.</t>
         </is>
@@ -3627,31 +4473,51 @@
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
+          <t>79 79 79 79</t>
+        </is>
+      </c>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>kommunen@kolding.dk</t>
+        </is>
+      </c>
+      <c r="J44" s="11" t="inlineStr">
+        <is>
+          <t>Nytorv 1, 6000 Kolding</t>
+        </is>
+      </c>
+      <c r="K44" s="14" t="inlineStr">
+        <is>
+          <t>https://www.kolding.dk/om-kommunen/intern-bygningsdrift/kontaktoplysninger</t>
+        </is>
+      </c>
+      <c r="L44" s="11" t="inlineStr">
+        <is>
           <t>Any day but Sunday at Søstrehuset (page)</t>
         </is>
       </c>
-      <c r="I44" s="11" t="inlineStr">
-        <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J44" s="17" t="inlineStr">
+      <c r="M44" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N44" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K44" s="11" t="inlineStr">
+      <c r="O44" s="11" t="inlineStr">
         <is>
           <t>Fly London (STN/LTN/LGW) to Billund BLL, approx 1h45. Car approx 40 min. Or CPH plus train 2h.</t>
         </is>
       </c>
-      <c r="L44" s="14" t="inlineStr">
+      <c r="P44" s="14" t="inlineStr">
         <is>
           <t>https://www.kolding.dk</t>
         </is>
       </c>
-      <c r="M44" s="11" t="inlineStr"/>
-      <c r="N44" s="11" t="inlineStr">
+      <c r="Q44" s="11" t="inlineStr"/>
+      <c r="R44" s="11" t="inlineStr">
         <is>
           <t>Explicitly marries out-of-town couples (free choice of municipality). Agencies name Kolding for speed.</t>
         </is>
@@ -3689,35 +4555,55 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>88 88 55 00</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J45" s="17" t="inlineStr">
+          <t>middelfart@middelfart.dk</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="inlineStr">
+        <is>
+          <t>Nytorv 9, 5500 Middelfart</t>
+        </is>
+      </c>
+      <c r="K45" s="14" t="inlineStr">
+        <is>
+          <t>https://www.middelfart.dk/Om%20kommunen/Kontakt%20via%20telefon%20og%20mail</t>
+        </is>
+      </c>
+      <c r="L45" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M45" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N45" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K45" s="11" t="inlineStr">
+      <c r="O45" s="11" t="inlineStr">
         <is>
           <t>Fly London (STN/LTN/LGW) to Billund BLL, approx 1h45. Car approx 45 min. Or CPH plus train 1h45.</t>
         </is>
       </c>
-      <c r="L45" s="14" t="inlineStr">
+      <c r="P45" s="14" t="inlineStr">
         <is>
           <t>https://www.middelfart.dk</t>
         </is>
       </c>
-      <c r="M45" s="14" t="inlineStr">
+      <c r="Q45" s="14" t="inlineStr">
         <is>
           <t>https://www.middelfart.dk/borgerservice/naar-i-vil-giftes</t>
         </is>
       </c>
-      <c r="N45" s="11" t="inlineStr">
+      <c r="R45" s="11" t="inlineStr">
         <is>
           <t>Free choice confirmed.</t>
         </is>
@@ -3755,35 +4641,55 @@
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>63 33 70 00</t>
         </is>
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J46" s="17" t="inlineStr">
+          <t>kommune@nyborg.dk</t>
+        </is>
+      </c>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>Rådhuset Torvet 1, 5800 Nyborg</t>
+        </is>
+      </c>
+      <c r="K46" s="14" t="inlineStr">
+        <is>
+          <t>https://www.nyborg.dk/da/om-kommunen/kontakt-og-aabningstider/</t>
+        </is>
+      </c>
+      <c r="L46" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M46" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N46" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K46" s="11" t="inlineStr">
+      <c r="O46" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to Nyborg approx 1h.</t>
         </is>
       </c>
-      <c r="L46" s="14" t="inlineStr">
+      <c r="P46" s="14" t="inlineStr">
         <is>
           <t>https://www.nyborg.dk</t>
         </is>
       </c>
-      <c r="M46" s="14" t="inlineStr">
+      <c r="Q46" s="14" t="inlineStr">
         <is>
           <t>https://www.nyborg.dk/da/borger-og-selvbetjening/personlige-forhold/vielse-og-skilsmisse/vielse-og-aegteskab/</t>
         </is>
       </c>
-      <c r="N46" s="11" t="inlineStr">
+      <c r="R46" s="11" t="inlineStr">
         <is>
           <t>Not restricted; closest Funen town hall to Copenhagen by train.</t>
         </is>
@@ -3821,35 +4727,55 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
+          <t>76 81 00 00</t>
+        </is>
+      </c>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>post@vejle.dk</t>
+        </is>
+      </c>
+      <c r="J47" s="11" t="inlineStr">
+        <is>
+          <t>Skolegade 1, 7100 Vejle</t>
+        </is>
+      </c>
+      <c r="K47" s="14" t="inlineStr">
+        <is>
+          <t>https://www.vejle.dk/da/om-os/kontakt-os/</t>
+        </is>
+      </c>
+      <c r="L47" s="11" t="inlineStr">
+        <is>
           <t>Mon 10-14, Fri 10-13, most Sat 10-11:30</t>
         </is>
       </c>
-      <c r="I47" s="11" t="inlineStr">
+      <c r="M47" s="11" t="inlineStr">
         <is>
           <t>Date fixed after certificate; no wait stated</t>
         </is>
       </c>
-      <c r="J47" s="17" t="inlineStr">
+      <c r="N47" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K47" s="11" t="inlineStr">
+      <c r="O47" s="11" t="inlineStr">
         <is>
           <t>Fly London (STN/LTN/LGW) to Billund BLL, approx 1h45. Car approx 30 min.</t>
         </is>
       </c>
-      <c r="L47" s="14" t="inlineStr">
+      <c r="P47" s="14" t="inlineStr">
         <is>
           <t>https://www.vejle.dk</t>
         </is>
       </c>
-      <c r="M47" s="14" t="inlineStr">
+      <c r="Q47" s="14" t="inlineStr">
         <is>
           <t>https://www.vejle.dk/da/service-og-selvbetjening/borger/borgerservice/vielse-aegteskab-og-skilsmisse/vielse-af-internationale-par-og-proevelsesattest/</t>
         </is>
       </c>
-      <c r="N47" s="11" t="inlineStr">
+      <c r="R47" s="11" t="inlineStr">
         <is>
           <t>Has a dedicated international-couples page.</t>
         </is>
@@ -3887,31 +4813,51 @@
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>72 32 00 00</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J48" s="17" t="inlineStr">
+          <t>borgerservice@hillerod.dk</t>
+        </is>
+      </c>
+      <c r="J48" s="11" t="inlineStr">
+        <is>
+          <t>Trollesmindealle 27, 3400 Hillerød</t>
+        </is>
+      </c>
+      <c r="K48" s="14" t="inlineStr">
+        <is>
+          <t>https://www.hillerod.dk/nyheder-og-fakta/kontakt/</t>
+        </is>
+      </c>
+      <c r="L48" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M48" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N48" s="17" t="inlineStr">
         <is>
           <t>Unknown (not researched: search quota ran out)</t>
         </is>
       </c>
-      <c r="K48" s="11" t="inlineStr">
+      <c r="O48" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. S-train to Hillerød approx 40 min.</t>
         </is>
       </c>
-      <c r="L48" s="14" t="inlineStr">
+      <c r="P48" s="14" t="inlineStr">
         <is>
           <t>https://www.hillerod.dk</t>
         </is>
       </c>
-      <c r="M48" s="11" t="inlineStr"/>
-      <c r="N48" s="11" t="inlineStr">
+      <c r="Q48" s="11" t="inlineStr"/>
+      <c r="R48" s="11" t="inlineStr">
         <is>
           <t>Regional sweep found no wedding details.</t>
         </is>
@@ -3949,31 +4895,51 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>36 39 36 39</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
+          <t>borgerservice@hvidovre.dk</t>
+        </is>
+      </c>
+      <c r="J49" s="11" t="inlineStr">
+        <is>
+          <t>Hvidovrevej 278, 2650 Hvidovre</t>
+        </is>
+      </c>
+      <c r="K49" s="14" t="inlineStr">
+        <is>
+          <t>https://www.hvidovre.dk/kontakt-os</t>
+        </is>
+      </c>
+      <c r="L49" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M49" s="11" t="inlineStr">
+        <is>
           <t>One agency names Hvidovre as a town hall that 'may have quicker availability'</t>
         </is>
       </c>
-      <c r="J49" s="17" t="inlineStr">
+      <c r="N49" s="17" t="inlineStr">
         <is>
           <t>Unknown (not researched: search quota ran out)</t>
         </is>
       </c>
-      <c r="K49" s="11" t="inlineStr">
+      <c r="O49" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. S-train to Hvidovre approx 20 min.</t>
         </is>
       </c>
-      <c r="L49" s="14" t="inlineStr">
+      <c r="P49" s="14" t="inlineStr">
         <is>
           <t>https://www.hvidovre.dk</t>
         </is>
       </c>
-      <c r="M49" s="11" t="inlineStr"/>
-      <c r="N49" s="11" t="inlineStr">
+      <c r="Q49" s="11" t="inlineStr"/>
+      <c r="R49" s="11" t="inlineStr">
         <is>
           <t>Worth a phone call: named by Wedding Planner Denmark as a quicker alternative.</t>
         </is>
@@ -4011,31 +4977,51 @@
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>48 49 00 00</t>
         </is>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J50" s="17" t="inlineStr">
+          <t>kommunen@horsholm.dk</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr">
+        <is>
+          <t>Slotsmarken 13, 2970 Hørsholm</t>
+        </is>
+      </c>
+      <c r="K50" s="14" t="inlineStr">
+        <is>
+          <t>https://www.horsholm.dk/om-kommunen/kontakt</t>
+        </is>
+      </c>
+      <c r="L50" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M50" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N50" s="17" t="inlineStr">
         <is>
           <t>Unknown (not researched: search quota ran out)</t>
         </is>
       </c>
-      <c r="K50" s="11" t="inlineStr">
+      <c r="O50" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to Rungsted Kyst approx 30 min.</t>
         </is>
       </c>
-      <c r="L50" s="14" t="inlineStr">
+      <c r="P50" s="14" t="inlineStr">
         <is>
           <t>https://www.horsholm.dk</t>
         </is>
       </c>
-      <c r="M50" s="11" t="inlineStr"/>
-      <c r="N50" s="11" t="inlineStr"/>
+      <c r="Q50" s="11" t="inlineStr"/>
+      <c r="R50" s="11" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="n">
@@ -4069,31 +5055,51 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>4357 7575</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J51" s="17" t="inlineStr">
+          <t>ishojkommune@ishoj.dk</t>
+        </is>
+      </c>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>Ishøj Rådhus, Ishøj Store Torv 20, 2635 Ishøj</t>
+        </is>
+      </c>
+      <c r="K51" s="14" t="inlineStr">
+        <is>
+          <t>https://ishoj.dk/om/kontakt-og-abningstider/</t>
+        </is>
+      </c>
+      <c r="L51" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M51" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N51" s="17" t="inlineStr">
         <is>
           <t>Unknown (not researched: search quota ran out)</t>
         </is>
       </c>
-      <c r="K51" s="11" t="inlineStr">
+      <c r="O51" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. S-train to Ishøj approx 25 min.</t>
         </is>
       </c>
-      <c r="L51" s="14" t="inlineStr">
+      <c r="P51" s="14" t="inlineStr">
         <is>
           <t>https://ishoj.dk</t>
         </is>
       </c>
-      <c r="M51" s="11" t="inlineStr"/>
-      <c r="N51" s="11" t="inlineStr"/>
+      <c r="Q51" s="11" t="inlineStr"/>
+      <c r="R51" s="11" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="n">
@@ -4127,31 +5133,51 @@
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>36 37 70 00</t>
         </is>
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J52" s="17" t="inlineStr">
+          <t>rk@rk.dk</t>
+        </is>
+      </c>
+      <c r="J52" s="11" t="inlineStr">
+        <is>
+          <t>Rødovre Parkvej 150, 2610 Rødovre</t>
+        </is>
+      </c>
+      <c r="K52" s="14" t="inlineStr">
+        <is>
+          <t>https://rk.dk/borger/om-kommunen/kontakt-og-aabningstider</t>
+        </is>
+      </c>
+      <c r="L52" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M52" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N52" s="17" t="inlineStr">
         <is>
           <t>Unknown (not researched: search quota ran out)</t>
         </is>
       </c>
-      <c r="K52" s="11" t="inlineStr">
+      <c r="O52" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. S-train/bus approx 25 min.</t>
         </is>
       </c>
-      <c r="L52" s="14" t="inlineStr">
+      <c r="P52" s="14" t="inlineStr">
         <is>
           <t>https://www.rk.dk</t>
         </is>
       </c>
-      <c r="M52" s="11" t="inlineStr"/>
-      <c r="N52" s="11" t="inlineStr"/>
+      <c r="Q52" s="11" t="inlineStr"/>
+      <c r="R52" s="11" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="n">
@@ -4185,31 +5211,51 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>47 97 40 00</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J53" s="17" t="inlineStr">
+          <t>kommune@vallensbaek.dk</t>
+        </is>
+      </c>
+      <c r="J53" s="11" t="inlineStr">
+        <is>
+          <t>Vallensbæk Stationstorv 100, 2665 Vallensbæk Strand</t>
+        </is>
+      </c>
+      <c r="K53" s="14" t="inlineStr">
+        <is>
+          <t>https://www.vallensbaek.dk/om-kommunen/kommunens-forvaltning</t>
+        </is>
+      </c>
+      <c r="L53" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M53" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N53" s="17" t="inlineStr">
         <is>
           <t>Unknown (not researched: search quota ran out)</t>
         </is>
       </c>
-      <c r="K53" s="11" t="inlineStr">
+      <c r="O53" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. S-train to Vallensbæk approx 25 min.</t>
         </is>
       </c>
-      <c r="L53" s="14" t="inlineStr">
+      <c r="P53" s="14" t="inlineStr">
         <is>
           <t>https://vallensbaek.dk</t>
         </is>
       </c>
-      <c r="M53" s="11" t="inlineStr"/>
-      <c r="N53" s="11" t="inlineStr"/>
+      <c r="Q53" s="11" t="inlineStr"/>
+      <c r="R53" s="11" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="n">
@@ -4243,31 +5289,51 @@
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>96117500</t>
         </is>
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J54" s="17" t="inlineStr">
+          <t>kommunen@holstebro.dk</t>
+        </is>
+      </c>
+      <c r="J54" s="11" t="inlineStr">
+        <is>
+          <t>Kirkestræde 11, 7500 Holstebro</t>
+        </is>
+      </c>
+      <c r="K54" s="14" t="inlineStr">
+        <is>
+          <t>https://www.holstebro.dk/kontakt</t>
+        </is>
+      </c>
+      <c r="L54" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M54" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N54" s="17" t="inlineStr">
         <is>
           <t>Unknown (not researched: search quota ran out)</t>
         </is>
       </c>
-      <c r="K54" s="11" t="inlineStr">
+      <c r="O54" s="11" t="inlineStr">
         <is>
           <t>Fly London (STN/LTN/LGW) to Billund BLL, approx 1h45. Car approx 1h20.</t>
         </is>
       </c>
-      <c r="L54" s="14" t="inlineStr">
+      <c r="P54" s="14" t="inlineStr">
         <is>
           <t>https://www.holstebro.dk</t>
         </is>
       </c>
-      <c r="M54" s="11" t="inlineStr"/>
-      <c r="N54" s="11" t="inlineStr"/>
+      <c r="Q54" s="11" t="inlineStr"/>
+      <c r="R54" s="11" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="n">
@@ -4301,31 +5367,51 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>96 63 12 00</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J55" s="17" t="inlineStr">
+          <t>borgerservice@lemvig.dk</t>
+        </is>
+      </c>
+      <c r="J55" s="11" t="inlineStr">
+        <is>
+          <t>Rådhusgade 2, 7620 Lemvig</t>
+        </is>
+      </c>
+      <c r="K55" s="14" t="inlineStr">
+        <is>
+          <t>https://lemvig.dk/kommunen/kontakt</t>
+        </is>
+      </c>
+      <c r="L55" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M55" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N55" s="17" t="inlineStr">
         <is>
           <t>Unknown (not researched: search quota ran out)</t>
         </is>
       </c>
-      <c r="K55" s="11" t="inlineStr">
+      <c r="O55" s="11" t="inlineStr">
         <is>
           <t>Fly London (STN/LTN/LGW) to Billund BLL, approx 1h45. Car approx 1h50.</t>
         </is>
       </c>
-      <c r="L55" s="14" t="inlineStr">
+      <c r="P55" s="14" t="inlineStr">
         <is>
           <t>https://www.lemvig.dk</t>
         </is>
       </c>
-      <c r="M55" s="11" t="inlineStr"/>
-      <c r="N55" s="11" t="inlineStr"/>
+      <c r="Q55" s="11" t="inlineStr"/>
+      <c r="R55" s="11" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="n">
@@ -4359,31 +5445,51 @@
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>87 80 33 33</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J56" s="17" t="inlineStr">
+          <t>odder.kommune@odder.dk</t>
+        </is>
+      </c>
+      <c r="J56" s="11" t="inlineStr">
+        <is>
+          <t>Rådhusgade 3, 8300 Odder</t>
+        </is>
+      </c>
+      <c r="K56" s="14" t="inlineStr">
+        <is>
+          <t>https://odder.dk/om-kommunen/kontakt-and-aabningstider/e-mail-and-telefonnumre/odder-raadhus</t>
+        </is>
+      </c>
+      <c r="L56" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M56" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N56" s="17" t="inlineStr">
         <is>
           <t>Unknown (not researched: search quota ran out)</t>
         </is>
       </c>
-      <c r="K56" s="11" t="inlineStr">
+      <c r="O56" s="11" t="inlineStr">
         <is>
           <t>Fly London STN to Aarhus AAR (Ryanair) approx 1h45, or Billund BLL. Car approx 45 min.</t>
         </is>
       </c>
-      <c r="L56" s="14" t="inlineStr">
+      <c r="P56" s="14" t="inlineStr">
         <is>
           <t>https://www.odder.dk</t>
         </is>
       </c>
-      <c r="M56" s="11" t="inlineStr"/>
-      <c r="N56" s="11" t="inlineStr"/>
+      <c r="Q56" s="11" t="inlineStr"/>
+      <c r="R56" s="11" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="n">
@@ -4417,31 +5523,51 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>87 92 22 00</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J57" s="17" t="inlineStr">
+          <t>kommune@samsoe.dk</t>
+        </is>
+      </c>
+      <c r="J57" s="11" t="inlineStr">
+        <is>
+          <t>Søtofte 10, 8305 Samsø</t>
+        </is>
+      </c>
+      <c r="K57" s="14" t="inlineStr">
+        <is>
+          <t>https://www.samsoe.dk/om-kommunen/kontakt-din-kommune</t>
+        </is>
+      </c>
+      <c r="L57" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M57" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N57" s="17" t="inlineStr">
         <is>
           <t>Unknown (not researched: search quota ran out)</t>
         </is>
       </c>
-      <c r="K57" s="11" t="inlineStr">
+      <c r="O57" s="11" t="inlineStr">
         <is>
           <t>Fly London STN to Aarhus AAR (Ryanair) approx 1h45, or Billund BLL. Ferry from Hou (1h) or Kalundborg.</t>
         </is>
       </c>
-      <c r="L57" s="14" t="inlineStr">
+      <c r="P57" s="14" t="inlineStr">
         <is>
           <t>https://www.samsoe.dk</t>
         </is>
       </c>
-      <c r="M57" s="11" t="inlineStr"/>
-      <c r="N57" s="11" t="inlineStr"/>
+      <c r="Q57" s="11" t="inlineStr"/>
+      <c r="R57" s="11" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="n">
@@ -4475,31 +5601,51 @@
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>99 15 55 00</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J58" s="17" t="inlineStr">
+          <t>sk@skivekommune.dk</t>
+        </is>
+      </c>
+      <c r="J58" s="11" t="inlineStr">
+        <is>
+          <t>Rådhuset, Torvegade 10, 7800 Skive</t>
+        </is>
+      </c>
+      <c r="K58" s="14" t="inlineStr">
+        <is>
+          <t>https://skive.dk/demokrati-og-kommune/raadhuse-og-medarbejdere/kontakt-kommunen/</t>
+        </is>
+      </c>
+      <c r="L58" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M58" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N58" s="17" t="inlineStr">
         <is>
           <t>Unknown (not researched: search quota ran out)</t>
         </is>
       </c>
-      <c r="K58" s="11" t="inlineStr">
+      <c r="O58" s="11" t="inlineStr">
         <is>
           <t>Fly London to Copenhagen CPH then 45 min hop to Aalborg AAL, or Billund BLL then approx 2h drive.</t>
         </is>
       </c>
-      <c r="L58" s="14" t="inlineStr">
+      <c r="P58" s="14" t="inlineStr">
         <is>
           <t>https://www.skive.dk</t>
         </is>
       </c>
-      <c r="M58" s="11" t="inlineStr"/>
-      <c r="N58" s="11" t="inlineStr"/>
+      <c r="Q58" s="11" t="inlineStr"/>
+      <c r="R58" s="11" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="n">
@@ -4533,31 +5679,51 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>+45 96 84 84 84</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J59" s="17" t="inlineStr">
+          <t>struer@struer.dk</t>
+        </is>
+      </c>
+      <c r="J59" s="11" t="inlineStr">
+        <is>
+          <t>Østergade 13-15, 7600 Struer</t>
+        </is>
+      </c>
+      <c r="K59" s="14" t="inlineStr">
+        <is>
+          <t>https://www.struer.dk/om-kommunen/kontakt-kommunen</t>
+        </is>
+      </c>
+      <c r="L59" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M59" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N59" s="17" t="inlineStr">
         <is>
           <t>Unknown (not researched: search quota ran out)</t>
         </is>
       </c>
-      <c r="K59" s="11" t="inlineStr">
+      <c r="O59" s="11" t="inlineStr">
         <is>
           <t>Fly London (STN/LTN/LGW) to Billund BLL, approx 1h45. Car approx 1h40.</t>
         </is>
       </c>
-      <c r="L59" s="14" t="inlineStr">
+      <c r="P59" s="14" t="inlineStr">
         <is>
           <t>https://www.struer.dk</t>
         </is>
       </c>
-      <c r="M59" s="11" t="inlineStr"/>
-      <c r="N59" s="11" t="inlineStr"/>
+      <c r="Q59" s="11" t="inlineStr"/>
+      <c r="R59" s="11" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="11" t="n">
@@ -4591,31 +5757,51 @@
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>72 57 77 77</t>
         </is>
       </c>
       <c r="I60" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J60" s="17" t="inlineStr">
+          <t>raadhus@jammerbugt.dk</t>
+        </is>
+      </c>
+      <c r="J60" s="11" t="inlineStr">
+        <is>
+          <t>Toftevej 43, 9440 Aabybro</t>
+        </is>
+      </c>
+      <c r="K60" s="14" t="inlineStr">
+        <is>
+          <t>https://www.jammerbugt.dk/borger/kontakt-og-abningstider/</t>
+        </is>
+      </c>
+      <c r="L60" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M60" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N60" s="17" t="inlineStr">
         <is>
           <t>Unknown (not researched: search quota ran out)</t>
         </is>
       </c>
-      <c r="K60" s="11" t="inlineStr">
+      <c r="O60" s="11" t="inlineStr">
         <is>
           <t>Fly London to Copenhagen CPH then 45 min hop to Aalborg AAL, or Billund BLL then approx 2h drive. Car 25 min from Aalborg.</t>
         </is>
       </c>
-      <c r="L60" s="14" t="inlineStr">
+      <c r="P60" s="14" t="inlineStr">
         <is>
           <t>https://www.jammerbugt.dk</t>
         </is>
       </c>
-      <c r="M60" s="11" t="inlineStr"/>
-      <c r="N60" s="11" t="inlineStr"/>
+      <c r="Q60" s="11" t="inlineStr"/>
+      <c r="R60" s="11" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="n">
@@ -4649,31 +5835,51 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>9621 3000</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J61" s="17" t="inlineStr">
+          <t>kommunen@laesoe.dk</t>
+        </is>
+      </c>
+      <c r="J61" s="11" t="inlineStr">
+        <is>
+          <t>Doktorvejen 2, DK-9940 Læsø</t>
+        </is>
+      </c>
+      <c r="K61" s="14" t="inlineStr">
+        <is>
+          <t>https://www.laesoe.dk/kommunen/kontakt-direkte-numre-til-kommunekontorets-ansatte</t>
+        </is>
+      </c>
+      <c r="L61" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M61" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N61" s="17" t="inlineStr">
         <is>
           <t>Unknown (not researched: search quota ran out)</t>
         </is>
       </c>
-      <c r="K61" s="11" t="inlineStr">
+      <c r="O61" s="11" t="inlineStr">
         <is>
           <t>Fly London to Copenhagen CPH then 45 min hop to Aalborg AAL, or Billund BLL then approx 2h drive. Ferry from Frederikshavn 90 min.</t>
         </is>
       </c>
-      <c r="L61" s="14" t="inlineStr">
+      <c r="P61" s="14" t="inlineStr">
         <is>
           <t>https://www.laesoe.dk</t>
         </is>
       </c>
-      <c r="M61" s="11" t="inlineStr"/>
-      <c r="N61" s="11" t="inlineStr"/>
+      <c r="Q61" s="11" t="inlineStr"/>
+      <c r="R61" s="11" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="n">
@@ -4707,31 +5913,51 @@
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>99 70 70 00</t>
         </is>
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J62" s="17" t="inlineStr">
+          <t>kommunen@morsoe.dk</t>
+        </is>
+      </c>
+      <c r="J62" s="11" t="inlineStr">
+        <is>
+          <t>Jernbanevej 7, 7900 Nykøbing Mors</t>
+        </is>
+      </c>
+      <c r="K62" s="14" t="inlineStr">
+        <is>
+          <t>https://mors.dk/</t>
+        </is>
+      </c>
+      <c r="L62" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M62" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N62" s="17" t="inlineStr">
         <is>
           <t>Unknown (not researched: search quota ran out)</t>
         </is>
       </c>
-      <c r="K62" s="11" t="inlineStr">
+      <c r="O62" s="11" t="inlineStr">
         <is>
           <t>Fly London to Copenhagen CPH then 45 min hop to Aalborg AAL, or Billund BLL then approx 2h drive. Car approx 1h20 from Aalborg.</t>
         </is>
       </c>
-      <c r="L62" s="14" t="inlineStr">
+      <c r="P62" s="14" t="inlineStr">
         <is>
           <t>https://www.morsoe.dk</t>
         </is>
       </c>
-      <c r="M62" s="11" t="inlineStr"/>
-      <c r="N62" s="11" t="inlineStr"/>
+      <c r="Q62" s="11" t="inlineStr"/>
+      <c r="R62" s="11" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="n">
@@ -4765,31 +5991,51 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>99 17 17 17</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J63" s="17" t="inlineStr">
+          <t>borgerservice@thisted.dk</t>
+        </is>
+      </c>
+      <c r="J63" s="11" t="inlineStr">
+        <is>
+          <t>Asylgade 30, 7700 Thisted</t>
+        </is>
+      </c>
+      <c r="K63" s="14" t="inlineStr">
+        <is>
+          <t>https://www.thisted.dk/om-kommunen/kontakt-og-aabningstider</t>
+        </is>
+      </c>
+      <c r="L63" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M63" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N63" s="17" t="inlineStr">
         <is>
           <t>Unknown (not researched: search quota ran out)</t>
         </is>
       </c>
-      <c r="K63" s="11" t="inlineStr">
+      <c r="O63" s="11" t="inlineStr">
         <is>
           <t>Fly London to Copenhagen CPH then 45 min hop to Aalborg AAL, or Billund BLL then approx 2h drive. Car approx 1h30 from Aalborg.</t>
         </is>
       </c>
-      <c r="L63" s="14" t="inlineStr">
+      <c r="P63" s="14" t="inlineStr">
         <is>
           <t>https://www.thisted.dk</t>
         </is>
       </c>
-      <c r="M63" s="11" t="inlineStr"/>
-      <c r="N63" s="11" t="inlineStr"/>
+      <c r="Q63" s="11" t="inlineStr"/>
+      <c r="R63" s="11" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="11" t="n">
@@ -4831,23 +6077,39 @@
           <t>not found</t>
         </is>
       </c>
-      <c r="J64" s="17" t="inlineStr">
+      <c r="J64" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K64" s="11" t="inlineStr"/>
+      <c r="L64" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M64" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N64" s="17" t="inlineStr">
         <is>
           <t>Unknown (not researched: search quota ran out)</t>
         </is>
       </c>
-      <c r="K64" s="11" t="inlineStr">
+      <c r="O64" s="11" t="inlineStr">
         <is>
           <t>Fly London to Copenhagen CPH then 45 min hop to Aalborg AAL, or Billund BLL then approx 2h drive. Car 45 min from Aalborg.</t>
         </is>
       </c>
-      <c r="L64" s="14" t="inlineStr">
+      <c r="P64" s="14" t="inlineStr">
         <is>
           <t>https://www.vesthimmerland.dk</t>
         </is>
       </c>
-      <c r="M64" s="11" t="inlineStr"/>
-      <c r="N64" s="11" t="inlineStr"/>
+      <c r="Q64" s="11" t="inlineStr"/>
+      <c r="R64" s="11" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="11" t="n">
@@ -4881,31 +6143,51 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>59 53 44 00</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J65" s="17" t="inlineStr">
+          <t>borgerservice@kalundborg.dk</t>
+        </is>
+      </c>
+      <c r="J65" s="11" t="inlineStr">
+        <is>
+          <t>Holbækvej 141B, 4400 Kalundborg</t>
+        </is>
+      </c>
+      <c r="K65" s="14" t="inlineStr">
+        <is>
+          <t>https://www.kalundborg.dk/kommunen/kontakt</t>
+        </is>
+      </c>
+      <c r="L65" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M65" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N65" s="17" t="inlineStr">
         <is>
           <t>Unknown (not researched: search quota ran out)</t>
         </is>
       </c>
-      <c r="K65" s="11" t="inlineStr">
+      <c r="O65" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to Kalundborg approx 1h40.</t>
         </is>
       </c>
-      <c r="L65" s="14" t="inlineStr">
+      <c r="P65" s="14" t="inlineStr">
         <is>
           <t>https://www.kalundborg.dk</t>
         </is>
       </c>
-      <c r="M65" s="11" t="inlineStr"/>
-      <c r="N65" s="11" t="inlineStr"/>
+      <c r="Q65" s="11" t="inlineStr"/>
+      <c r="R65" s="11" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="11" t="n">
@@ -4939,31 +6221,51 @@
       </c>
       <c r="H66" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>+45 46464646</t>
         </is>
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J66" s="17" t="inlineStr">
+          <t>post@lejre.dk</t>
+        </is>
+      </c>
+      <c r="J66" s="11" t="inlineStr">
+        <is>
+          <t>Lejrevej 15, 4320 Lejre (also Møllebjergvej 4, 4330 Hvalsø)</t>
+        </is>
+      </c>
+      <c r="K66" s="14" t="inlineStr">
+        <is>
+          <t>https://lejre.dk/kontakt</t>
+        </is>
+      </c>
+      <c r="L66" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M66" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N66" s="17" t="inlineStr">
         <is>
           <t>Unknown (not researched: search quota ran out)</t>
         </is>
       </c>
-      <c r="K66" s="11" t="inlineStr">
+      <c r="O66" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to Hvalsø approx 45 min.</t>
         </is>
       </c>
-      <c r="L66" s="14" t="inlineStr">
+      <c r="P66" s="14" t="inlineStr">
         <is>
           <t>https://www.lejre.dk</t>
         </is>
       </c>
-      <c r="M66" s="11" t="inlineStr"/>
-      <c r="N66" s="11" t="inlineStr"/>
+      <c r="Q66" s="11" t="inlineStr"/>
+      <c r="R66" s="11" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="11" t="n">
@@ -4997,31 +6299,51 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>59 66 66 66</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J67" s="17" t="inlineStr">
+          <t>kommune@odsherred.dk</t>
+        </is>
+      </c>
+      <c r="J67" s="11" t="inlineStr">
+        <is>
+          <t>Nyvej 22, 4573 Højby</t>
+        </is>
+      </c>
+      <c r="K67" s="14" t="inlineStr">
+        <is>
+          <t>https://www.odsherred.dk/da/se-mere-om-kommunen/kontakt/</t>
+        </is>
+      </c>
+      <c r="L67" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M67" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N67" s="17" t="inlineStr">
         <is>
           <t>Unknown (not researched: search quota ran out)</t>
         </is>
       </c>
-      <c r="K67" s="11" t="inlineStr">
+      <c r="O67" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train via Holbæk approx 1h40.</t>
         </is>
       </c>
-      <c r="L67" s="14" t="inlineStr">
+      <c r="P67" s="14" t="inlineStr">
         <is>
           <t>https://www.odsherred.dk</t>
         </is>
       </c>
-      <c r="M67" s="11" t="inlineStr"/>
-      <c r="N67" s="11" t="inlineStr"/>
+      <c r="Q67" s="11" t="inlineStr"/>
+      <c r="R67" s="11" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="n">
@@ -5055,31 +6377,51 @@
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>58573600</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J68" s="17" t="inlineStr">
+          <t>slagelse@slagelse.dk</t>
+        </is>
+      </c>
+      <c r="J68" s="11" t="inlineStr">
+        <is>
+          <t>Rådhuspladsen 11, 4200 Slagelse</t>
+        </is>
+      </c>
+      <c r="K68" s="14" t="inlineStr">
+        <is>
+          <t>https://www.slagelse.dk/da/om-kommunen/kontakt/kontakt-slagelse-kommune/</t>
+        </is>
+      </c>
+      <c r="L68" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M68" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N68" s="17" t="inlineStr">
         <is>
           <t>Unknown (not researched: search quota ran out)</t>
         </is>
       </c>
-      <c r="K68" s="11" t="inlineStr">
+      <c r="O68" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to Slagelse approx 1h.</t>
         </is>
       </c>
-      <c r="L68" s="14" t="inlineStr">
+      <c r="P68" s="14" t="inlineStr">
         <is>
           <t>https://www.slagelse.dk</t>
         </is>
       </c>
-      <c r="M68" s="11" t="inlineStr"/>
-      <c r="N68" s="11" t="inlineStr"/>
+      <c r="Q68" s="11" t="inlineStr"/>
+      <c r="R68" s="11" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="n">
@@ -5113,31 +6455,51 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>57 87 60 00</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J69" s="17" t="inlineStr">
+          <t>borgerservice@soroe.dk</t>
+        </is>
+      </c>
+      <c r="J69" s="11" t="inlineStr">
+        <is>
+          <t>Rådhusvej 8, 4180 Sorø (indgang og parkering fra Absalonsgade 17)</t>
+        </is>
+      </c>
+      <c r="K69" s="14" t="inlineStr">
+        <is>
+          <t>https://soroe.dk/kontakt</t>
+        </is>
+      </c>
+      <c r="L69" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M69" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N69" s="17" t="inlineStr">
         <is>
           <t>Unknown (not researched: search quota ran out)</t>
         </is>
       </c>
-      <c r="K69" s="11" t="inlineStr">
+      <c r="O69" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to Sorø approx 50 min.</t>
         </is>
       </c>
-      <c r="L69" s="14" t="inlineStr">
+      <c r="P69" s="14" t="inlineStr">
         <is>
           <t>https://soroe.dk</t>
         </is>
       </c>
-      <c r="M69" s="11" t="inlineStr"/>
-      <c r="N69" s="11" t="inlineStr"/>
+      <c r="Q69" s="11" t="inlineStr"/>
+      <c r="R69" s="11" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="11" t="n">
@@ -5171,31 +6533,51 @@
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>76 66 06 60</t>
         </is>
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J70" s="17" t="inlineStr">
+          <t>raadhuset@fanoe.dk</t>
+        </is>
+      </c>
+      <c r="J70" s="11" t="inlineStr">
+        <is>
+          <t>Skolevej 5, Nordby, 6720 Fanø</t>
+        </is>
+      </c>
+      <c r="K70" s="14" t="inlineStr">
+        <is>
+          <t>https://fanoe.dk/kommunen/kontakt</t>
+        </is>
+      </c>
+      <c r="L70" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M70" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N70" s="17" t="inlineStr">
         <is>
           <t>Unknown (not researched: search quota ran out)</t>
         </is>
       </c>
-      <c r="K70" s="11" t="inlineStr">
+      <c r="O70" s="11" t="inlineStr">
         <is>
           <t>Fly London (STN/LTN/LGW) to Billund BLL, approx 1h45. Approx 1h to Esbjerg then 12-min ferry.</t>
         </is>
       </c>
-      <c r="L70" s="14" t="inlineStr">
+      <c r="P70" s="14" t="inlineStr">
         <is>
           <t>https://www.fanoe.dk</t>
         </is>
       </c>
-      <c r="M70" s="11" t="inlineStr"/>
-      <c r="N70" s="11" t="inlineStr"/>
+      <c r="Q70" s="11" t="inlineStr"/>
+      <c r="R70" s="11" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="11" t="n">
@@ -5229,31 +6611,51 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>64 82 82 82</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="J71" s="17" t="inlineStr">
+          <t>post@nordfynskommune.dk</t>
+        </is>
+      </c>
+      <c r="J71" s="11" t="inlineStr">
+        <is>
+          <t>Østergade 23, 5400 Bogense (Nordfyns Kommune town hall). Also listed: Rådhuspladsen 2, 5450 Otterup (tel. 64 82 80 90).</t>
+        </is>
+      </c>
+      <c r="K71" s="14" t="inlineStr">
+        <is>
+          <t>https://www.nordfynskommune.dk/vores-kommune/kontakt-os/</t>
+        </is>
+      </c>
+      <c r="L71" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M71" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="N71" s="17" t="inlineStr">
         <is>
           <t>Unknown (not researched: search quota ran out)</t>
         </is>
       </c>
-      <c r="K71" s="11" t="inlineStr">
+      <c r="O71" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to Odense 1h15 then bus 40 min.</t>
         </is>
       </c>
-      <c r="L71" s="14" t="inlineStr">
+      <c r="P71" s="14" t="inlineStr">
         <is>
           <t>https://www.nordfynskommune.dk</t>
         </is>
       </c>
-      <c r="M71" s="11" t="inlineStr"/>
-      <c r="N71" s="11" t="inlineStr"/>
+      <c r="Q71" s="11" t="inlineStr"/>
+      <c r="R71" s="11" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="11" t="n">
@@ -5292,26 +6694,42 @@
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
+          <t>vielser@balk.dk</t>
+        </is>
+      </c>
+      <c r="J72" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K72" s="11" t="inlineStr"/>
+      <c r="L72" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M72" s="11" t="inlineStr">
+        <is>
           <t>Own page: request no later than 3 weeks before the wedding date, so earliest approx 8-9 Oct</t>
         </is>
       </c>
-      <c r="J72" s="18" t="inlineStr">
+      <c r="N72" s="18" t="inlineStr">
         <is>
           <t>Unlikely</t>
         </is>
       </c>
-      <c r="K72" s="11" t="inlineStr">
+      <c r="O72" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. S-train to Ballerup approx 35 min.</t>
         </is>
       </c>
-      <c r="L72" s="14" t="inlineStr">
+      <c r="P72" s="14" t="inlineStr">
         <is>
           <t>https://ballerup.dk</t>
         </is>
       </c>
-      <c r="M72" s="11" t="inlineStr"/>
-      <c r="N72" s="11" t="inlineStr">
+      <c r="Q72" s="11" t="inlineStr"/>
+      <c r="R72" s="11" t="inlineStr">
         <is>
           <t>3-week rule puts a request made now just outside the window. Worth one phone call only.</t>
         </is>
@@ -5349,31 +6767,47 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>vielse@brk.dk</t>
+        </is>
+      </c>
+      <c r="J73" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K73" s="11" t="inlineStr"/>
+      <c r="L73" s="11" t="inlineStr">
+        <is>
           <t>Thu, Fri and selected Saturdays (agency reports)</t>
         </is>
       </c>
-      <c r="I73" s="11" t="inlineStr">
+      <c r="M73" s="11" t="inlineStr">
         <is>
           <t>Stopped taking new foreign-couple bookings around 21 July 2026 for capacity reasons; wants requests 14 days to 1 month ahead</t>
         </is>
       </c>
-      <c r="J73" s="18" t="inlineStr">
+      <c r="N73" s="18" t="inlineStr">
         <is>
           <t>Unlikely</t>
         </is>
       </c>
-      <c r="K73" s="11" t="inlineStr">
+      <c r="O73" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Then flight CPH to Rønne 35 min, or train to Ystad plus ferry.</t>
         </is>
       </c>
-      <c r="L73" s="14" t="inlineStr">
+      <c r="P73" s="14" t="inlineStr">
         <is>
           <t>https://www.brk.dk</t>
         </is>
       </c>
-      <c r="M73" s="11" t="inlineStr"/>
-      <c r="N73" s="11" t="inlineStr">
+      <c r="Q73" s="11" t="inlineStr"/>
+      <c r="R73" s="11" t="inlineStr">
         <is>
           <t>Historically over half of Bornholm's civil weddings were foreign couples; capacity closed summer 2026.</t>
         </is>
@@ -5411,35 +6845,55 @@
       </c>
       <c r="H74" s="11" t="inlineStr">
         <is>
+          <t>32 89 01 00</t>
+        </is>
+      </c>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>borgerservice@dragoer.dk</t>
+        </is>
+      </c>
+      <c r="J74" s="11" t="inlineStr">
+        <is>
+          <t>Kirkevej 7, 2791 Dragør</t>
+        </is>
+      </c>
+      <c r="K74" s="14" t="inlineStr">
+        <is>
+          <t>https://www.dragoer.dk/om-kommunen/kontakt/kontakt-og-aabningstider</t>
+        </is>
+      </c>
+      <c r="L74" s="11" t="inlineStr">
+        <is>
           <t>Selected days each month 10:30-16:30 plus selected Saturdays; agencies say foreign couples get Thursdays only (Thu 1 Oct)</t>
         </is>
       </c>
-      <c r="I74" s="11" t="inlineStr">
+      <c r="M74" s="11" t="inlineStr">
         <is>
           <t>Office is one person; replies can take up to 2 weeks</t>
         </is>
       </c>
-      <c r="J74" s="18" t="inlineStr">
+      <c r="N74" s="18" t="inlineStr">
         <is>
           <t>Unlikely</t>
         </is>
       </c>
-      <c r="K74" s="11" t="inlineStr">
+      <c r="O74" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Bus 35 from airport approx 15 min.</t>
         </is>
       </c>
-      <c r="L74" s="14" t="inlineStr">
+      <c r="P74" s="14" t="inlineStr">
         <is>
           <t>https://www.dragoer.dk</t>
         </is>
       </c>
-      <c r="M74" s="14" t="inlineStr">
+      <c r="Q74" s="14" t="inlineStr">
         <is>
           <t>https://www.dragoer.dk/voksne-og-aeldre/vielse-og-skilsmisse/naar-i-vil-giftes</t>
         </is>
       </c>
-      <c r="N74" s="11" t="inlineStr">
+      <c r="R74" s="11" t="inlineStr">
         <is>
           <t>Marries non-residents. Only realistic date Thu 1 Oct and slow replies.</t>
         </is>
@@ -5477,31 +6931,51 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
+          <t>38 21 00 00</t>
+        </is>
+      </c>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>borgerservice@frederiksberg.dk</t>
+        </is>
+      </c>
+      <c r="J75" s="11" t="inlineStr">
+        <is>
+          <t>Frederiksberg Rådhus, Smallegade 1, 2000 Frederiksberg</t>
+        </is>
+      </c>
+      <c r="K75" s="14" t="inlineStr">
+        <is>
+          <t>https://www.frederiksberg.dk/kommunen/forvaltning-og-fakta-om-kommunen/kontakt</t>
+        </is>
+      </c>
+      <c r="L75" s="11" t="inlineStr">
+        <is>
           <t>Thursdays (2026 guides)</t>
         </is>
       </c>
-      <c r="I75" s="11" t="inlineStr">
+      <c r="M75" s="11" t="inlineStr">
         <is>
           <t>Reduced capacity for international couples; next available international date reported months out</t>
         </is>
       </c>
-      <c r="J75" s="18" t="inlineStr">
+      <c r="N75" s="18" t="inlineStr">
         <is>
           <t>Unlikely</t>
         </is>
       </c>
-      <c r="K75" s="11" t="inlineStr">
+      <c r="O75" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Metro to Frederiksberg approx 25 min.</t>
         </is>
       </c>
-      <c r="L75" s="14" t="inlineStr">
+      <c r="P75" s="14" t="inlineStr">
         <is>
           <t>https://www.frederiksberg.dk</t>
         </is>
       </c>
-      <c r="M75" s="11" t="inlineStr"/>
-      <c r="N75" s="11" t="inlineStr">
+      <c r="Q75" s="11" t="inlineStr"/>
+      <c r="R75" s="11" t="inlineStr">
         <is>
           <t>Copenhagen overflow; agencies report long waits.</t>
         </is>
@@ -5539,35 +7013,55 @@
       </c>
       <c r="H76" s="11" t="inlineStr">
         <is>
+          <t>39 57 50 00</t>
+        </is>
+      </c>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>kommunen@gladsaxe.dk</t>
+        </is>
+      </c>
+      <c r="J76" s="11" t="inlineStr">
+        <is>
+          <t>Rådhus Allé 7, 2860 Søborg</t>
+        </is>
+      </c>
+      <c r="K76" s="14" t="inlineStr">
+        <is>
+          <t>https://gladsaxe.dk/kommunen/om-gladsaxe-kommune/kontakt-os</t>
+        </is>
+      </c>
+      <c r="L76" s="11" t="inlineStr">
+        <is>
           <t>All weekdays in opening hours; Sat from 10:30</t>
         </is>
       </c>
-      <c r="I76" s="11" t="inlineStr">
+      <c r="M76" s="11" t="inlineStr">
         <is>
           <t>Municipality states no waiting time, but agencies report approx 8-9 weeks backlog as Copenhagen overflow</t>
         </is>
       </c>
-      <c r="J76" s="18" t="inlineStr">
+      <c r="N76" s="18" t="inlineStr">
         <is>
           <t>Unlikely</t>
         </is>
       </c>
-      <c r="K76" s="11" t="inlineStr">
+      <c r="O76" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Bus/S-train to Buddinge approx 30 min.</t>
         </is>
       </c>
-      <c r="L76" s="14" t="inlineStr">
+      <c r="P76" s="14" t="inlineStr">
         <is>
           <t>https://gladsaxe.dk</t>
         </is>
       </c>
-      <c r="M76" s="14" t="inlineStr">
+      <c r="Q76" s="14" t="inlineStr">
         <is>
           <t>https://gladsaxe.dk/borger/borgerservice/vielse-og-skilsmisse/aegteskab</t>
         </is>
       </c>
-      <c r="N76" s="11" t="inlineStr">
+      <c r="R76" s="11" t="inlineStr">
         <is>
           <t>Marries non-residents on weekdays. Conflicting availability reports.</t>
         </is>
@@ -5605,31 +7099,51 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
+          <t>4452 7060</t>
+        </is>
+      </c>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>borgerservice@herlev.dk</t>
+        </is>
+      </c>
+      <c r="J77" s="11" t="inlineStr">
+        <is>
+          <t>Herlev Hovedgade 110, 1. sal, 2730 Herlev</t>
+        </is>
+      </c>
+      <c r="K77" s="14" t="inlineStr">
+        <is>
+          <t>https://www.herlev.dk/kontakt</t>
+        </is>
+      </c>
+      <c r="L77" s="11" t="inlineStr">
+        <is>
           <t>Mon, Wed, Fri 10-14; every other Saturday 10:00</t>
         </is>
       </c>
-      <c r="I77" s="11" t="inlineStr">
+      <c r="M77" s="11" t="inlineStr">
         <is>
           <t>Agency report: 8-9 weeks waiting, dates fill weeks ahead</t>
         </is>
       </c>
-      <c r="J77" s="18" t="inlineStr">
+      <c r="N77" s="18" t="inlineStr">
         <is>
           <t>Unlikely</t>
         </is>
       </c>
-      <c r="K77" s="11" t="inlineStr">
+      <c r="O77" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. S-train to Herlev approx 25 min.</t>
         </is>
       </c>
-      <c r="L77" s="14" t="inlineStr">
+      <c r="P77" s="14" t="inlineStr">
         <is>
           <t>https://herlev.dk</t>
         </is>
       </c>
-      <c r="M77" s="11" t="inlineStr"/>
-      <c r="N77" s="11" t="inlineStr">
+      <c r="Q77" s="11" t="inlineStr"/>
+      <c r="R77" s="11" t="inlineStr">
         <is>
           <t>Clearly marries non-residents; only a cancellation would fit.</t>
         </is>
@@ -5667,31 +7181,47 @@
       </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>+45 99 60 40 00</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
+          <t>post@ikast-brande.dk</t>
+        </is>
+      </c>
+      <c r="J78" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K78" s="11" t="inlineStr"/>
+      <c r="L78" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M78" s="11" t="inlineStr">
+        <is>
           <t>Date set only after original documents are approved in person</t>
         </is>
       </c>
-      <c r="J78" s="18" t="inlineStr">
+      <c r="N78" s="18" t="inlineStr">
         <is>
           <t>Unlikely</t>
         </is>
       </c>
-      <c r="K78" s="11" t="inlineStr">
+      <c r="O78" s="11" t="inlineStr">
         <is>
           <t>Fly London (STN/LTN/LGW) to Billund BLL, approx 1h45. Car approx 45 min.</t>
         </is>
       </c>
-      <c r="L78" s="14" t="inlineStr">
+      <c r="P78" s="14" t="inlineStr">
         <is>
           <t>https://www.ikast-brande.dk</t>
         </is>
       </c>
-      <c r="M78" s="11" t="inlineStr"/>
-      <c r="N78" s="11" t="inlineStr">
+      <c r="Q78" s="11" t="inlineStr"/>
+      <c r="R78" s="11" t="inlineStr">
         <is>
           <t>In-person step before any date.</t>
         </is>
@@ -5729,35 +7259,55 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
+          <t>72 33 33 33</t>
+        </is>
+      </c>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>hjoerring@hjoerring.dk</t>
+        </is>
+      </c>
+      <c r="J79" s="11" t="inlineStr">
+        <is>
+          <t>Springvandspladsen 5, 9800 Hjørring</t>
+        </is>
+      </c>
+      <c r="K79" s="14" t="inlineStr">
+        <is>
+          <t>https://hjoerring.dk/kontakt</t>
+        </is>
+      </c>
+      <c r="L79" s="11" t="inlineStr">
+        <is>
           <t>Fri and Sat 9:30-11:30</t>
         </is>
       </c>
-      <c r="I79" s="11" t="inlineStr">
+      <c r="M79" s="11" t="inlineStr">
         <is>
           <t>Approx 14 days processing</t>
         </is>
       </c>
-      <c r="J79" s="18" t="inlineStr">
+      <c r="N79" s="18" t="inlineStr">
         <is>
           <t>Unlikely</t>
         </is>
       </c>
-      <c r="K79" s="11" t="inlineStr">
+      <c r="O79" s="11" t="inlineStr">
         <is>
           <t>Fly London to Copenhagen CPH then 45 min hop to Aalborg AAL, or Billund BLL then approx 2h drive. Car approx 45 min from Aalborg.</t>
         </is>
       </c>
-      <c r="L79" s="14" t="inlineStr">
+      <c r="P79" s="14" t="inlineStr">
         <is>
           <t>https://hjoerring.dk</t>
         </is>
       </c>
-      <c r="M79" s="14" t="inlineStr">
+      <c r="Q79" s="14" t="inlineStr">
         <is>
           <t>https://hjoerring.dk/borger/borgerservice/aegteskab-og-parforhold/vielse</t>
         </is>
       </c>
-      <c r="N79" s="11" t="inlineStr"/>
+      <c r="R79" s="11" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="11" t="n">
@@ -5791,35 +7341,55 @@
       </c>
       <c r="H80" s="11" t="inlineStr">
         <is>
+          <t>5667 6767</t>
+        </is>
+      </c>
+      <c r="I80" s="11" t="inlineStr">
+        <is>
+          <t>raadhus@koege.dk</t>
+        </is>
+      </c>
+      <c r="J80" s="11" t="inlineStr">
+        <is>
+          <t>Rådhuset, Torvet 1, 4600 Køge</t>
+        </is>
+      </c>
+      <c r="K80" s="14" t="inlineStr">
+        <is>
+          <t>https://www.koege.dk/om-koege-kommune/kontakt-os</t>
+        </is>
+      </c>
+      <c r="L80" s="11" t="inlineStr">
+        <is>
           <t>Weekdays plus some Saturdays</t>
         </is>
       </c>
-      <c r="I80" s="11" t="inlineStr">
+      <c r="M80" s="11" t="inlineStr">
         <is>
           <t>14 days processing quoted</t>
         </is>
       </c>
-      <c r="J80" s="18" t="inlineStr">
+      <c r="N80" s="18" t="inlineStr">
         <is>
           <t>Unlikely</t>
         </is>
       </c>
-      <c r="K80" s="11" t="inlineStr">
+      <c r="O80" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. S-train to Køge approx 45 min.</t>
         </is>
       </c>
-      <c r="L80" s="14" t="inlineStr">
+      <c r="P80" s="14" t="inlineStr">
         <is>
           <t>https://www.koege.dk</t>
         </is>
       </c>
-      <c r="M80" s="14" t="inlineStr">
+      <c r="Q80" s="14" t="inlineStr">
         <is>
           <t>https://www.koege.dk/borger/bestil-tid-i-borgerservice/vielse-og-aegteskab</t>
         </is>
       </c>
-      <c r="N80" s="11" t="inlineStr">
+      <c r="R80" s="11" t="inlineStr">
         <is>
           <t>14-day processing leaves little room.</t>
         </is>
@@ -5857,35 +7427,55 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
+          <t>55 88 55 88</t>
+        </is>
+      </c>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>borgerservice@naestved.dk</t>
+        </is>
+      </c>
+      <c r="J81" s="11" t="inlineStr">
+        <is>
+          <t>Rådmandshaven 20, 4700 Næstved</t>
+        </is>
+      </c>
+      <c r="K81" s="14" t="inlineStr">
+        <is>
+          <t>https://www.naestved.dk/kommunen/kontakt-naestved-kommune</t>
+        </is>
+      </c>
+      <c r="L81" s="11" t="inlineStr">
+        <is>
           <t>15-min ceremonies</t>
         </is>
       </c>
-      <c r="I81" s="11" t="inlineStr">
+      <c r="M81" s="11" t="inlineStr">
         <is>
           <t>Approx 4 weeks processing</t>
         </is>
       </c>
-      <c r="J81" s="18" t="inlineStr">
+      <c r="N81" s="18" t="inlineStr">
         <is>
           <t>Unlikely</t>
         </is>
       </c>
-      <c r="K81" s="11" t="inlineStr">
+      <c r="O81" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to Næstved approx 1h.</t>
         </is>
       </c>
-      <c r="L81" s="14" t="inlineStr">
+      <c r="P81" s="14" t="inlineStr">
         <is>
           <t>https://www.naestved.dk</t>
         </is>
       </c>
-      <c r="M81" s="14" t="inlineStr">
+      <c r="Q81" s="14" t="inlineStr">
         <is>
           <t>https://www.naestved.dk/borgerservice/naar-i-skal-giftes</t>
         </is>
       </c>
-      <c r="N81" s="11" t="inlineStr"/>
+      <c r="R81" s="11" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="11" t="n">
@@ -5919,35 +7509,55 @@
       </c>
       <c r="H82" s="11" t="inlineStr">
         <is>
+          <t>56 18 20 50</t>
+        </is>
+      </c>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>borgerservice@solrod.dk</t>
+        </is>
+      </c>
+      <c r="J82" s="11" t="inlineStr">
+        <is>
+          <t>Solrød Center 1, 2680 Solrød Strand</t>
+        </is>
+      </c>
+      <c r="K82" s="14" t="inlineStr">
+        <is>
+          <t>https://solrod.dk/kommunen/kontakt</t>
+        </is>
+      </c>
+      <c r="L82" s="11" t="inlineStr">
+        <is>
           <t>Mon-Tue 10-15, Thu 10-17</t>
         </is>
       </c>
-      <c r="I82" s="11" t="inlineStr">
+      <c r="M82" s="11" t="inlineStr">
         <is>
           <t>3-4 weeks processing</t>
         </is>
       </c>
-      <c r="J82" s="18" t="inlineStr">
+      <c r="N82" s="18" t="inlineStr">
         <is>
           <t>Unlikely</t>
         </is>
       </c>
-      <c r="K82" s="11" t="inlineStr">
+      <c r="O82" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. S-train to Solrød Strand approx 35 min.</t>
         </is>
       </c>
-      <c r="L82" s="14" t="inlineStr">
+      <c r="P82" s="14" t="inlineStr">
         <is>
           <t>https://www.solrod.dk</t>
         </is>
       </c>
-      <c r="M82" s="14" t="inlineStr">
+      <c r="Q82" s="14" t="inlineStr">
         <is>
           <t>https://www.solrod.dk/service-og-selvbetjening/borgerservice/vielse</t>
         </is>
       </c>
-      <c r="N82" s="11" t="inlineStr"/>
+      <c r="R82" s="11" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="11" t="n">
@@ -5981,31 +7591,47 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>+45 63 51 60 00</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
+          <t>post@langelandkommune.dk</t>
+        </is>
+      </c>
+      <c r="J83" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K83" s="11" t="inlineStr"/>
+      <c r="L83" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M83" s="11" t="inlineStr">
+        <is>
           <t>One of the four busiest wedding-tourism municipalities (with Tønder, Ærø, Copenhagen)</t>
         </is>
       </c>
-      <c r="J83" s="18" t="inlineStr">
+      <c r="N83" s="18" t="inlineStr">
         <is>
           <t>Unlikely</t>
         </is>
       </c>
-      <c r="K83" s="11" t="inlineStr">
+      <c r="O83" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to Svendborg 2h then bus over the bridge 30 min.</t>
         </is>
       </c>
-      <c r="L83" s="14" t="inlineStr">
+      <c r="P83" s="14" t="inlineStr">
         <is>
           <t>https://www.langelandkommune.dk</t>
         </is>
       </c>
-      <c r="M83" s="11" t="inlineStr"/>
-      <c r="N83" s="11" t="inlineStr">
+      <c r="Q83" s="11" t="inlineStr"/>
+      <c r="R83" s="11" t="inlineStr">
         <is>
           <t>High demand destination.</t>
         </is>
@@ -6043,35 +7669,55 @@
       </c>
       <c r="H84" s="11" t="inlineStr">
         <is>
+          <t>66 13 13 72</t>
+        </is>
+      </c>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>kontakt@odense.dk</t>
+        </is>
+      </c>
+      <c r="J84" s="11" t="inlineStr">
+        <is>
+          <t>Flakhaven 2, 5000 Odense C</t>
+        </is>
+      </c>
+      <c r="K84" s="14" t="inlineStr">
+        <is>
+          <t>https://www.odense.dk/om-kommunen/forvaltninger/beskaeftigelses-og-socialforvaltningen/kontaktcenter-odense-kommune</t>
+        </is>
+      </c>
+      <c r="L84" s="11" t="inlineStr">
+        <is>
           <t>All weekdays plus Saturdays from 10:00</t>
         </is>
       </c>
-      <c r="I84" s="11" t="inlineStr">
+      <c r="M84" s="11" t="inlineStr">
         <is>
           <t>Declaration must be in at least 14 days before the date</t>
         </is>
       </c>
-      <c r="J84" s="18" t="inlineStr">
+      <c r="N84" s="18" t="inlineStr">
         <is>
           <t>Unlikely</t>
         </is>
       </c>
-      <c r="K84" s="11" t="inlineStr">
+      <c r="O84" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to Odense approx 1h15.</t>
         </is>
       </c>
-      <c r="L84" s="14" t="inlineStr">
+      <c r="P84" s="14" t="inlineStr">
         <is>
           <t>https://www.odense.dk</t>
         </is>
       </c>
-      <c r="M84" s="14" t="inlineStr">
+      <c r="Q84" s="14" t="inlineStr">
         <is>
           <t>https://www.odense.dk/borger/borgerservice/vielse/borgerlig-vielse</t>
         </is>
       </c>
-      <c r="N84" s="11" t="inlineStr">
+      <c r="R84" s="11" t="inlineStr">
         <is>
           <t>14-day rule and city demand.</t>
         </is>
@@ -6113,35 +7759,51 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
+          <t>+45 63 52 50 00</t>
+        </is>
+      </c>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>info@weddinginfo.dk</t>
+        </is>
+      </c>
+      <c r="J85" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K85" s="11" t="inlineStr"/>
+      <c r="L85" s="11" t="inlineStr">
+        <is>
           <t>Weekdays; approx 200 dates a year</t>
         </is>
       </c>
-      <c r="I85" s="11" t="inlineStr">
+      <c r="M85" s="11" t="inlineStr">
         <is>
           <t>Typically offers a date 7-8 weeks out; AUTO-REPLY 17 Sep: answer within 3-5 working days</t>
         </is>
       </c>
-      <c r="J85" s="18" t="inlineStr">
+      <c r="N85" s="18" t="inlineStr">
         <is>
           <t>Unlikely</t>
         </is>
       </c>
-      <c r="K85" s="11" t="inlineStr">
+      <c r="O85" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to Svendborg 2h then ferry 75 min.</t>
         </is>
       </c>
-      <c r="L85" s="14" t="inlineStr">
+      <c r="P85" s="14" t="inlineStr">
         <is>
           <t>https://www.aeroekommune.dk</t>
         </is>
       </c>
-      <c r="M85" s="14" t="inlineStr">
+      <c r="Q85" s="14" t="inlineStr">
         <is>
           <t>https://www.aeroekommune.dk/mit-liv/borgerservice/aegteskab-heirat-marriage/aegteskab-vielse</t>
         </is>
       </c>
-      <c r="N85" s="11" t="inlineStr">
+      <c r="R85" s="11" t="inlineStr">
         <is>
           <t>Email sent; awaiting reply.</t>
         </is>
@@ -6179,35 +7841,51 @@
       </c>
       <c r="H86" s="11" t="inlineStr">
         <is>
+          <t>+45 72 59 60 00</t>
+        </is>
+      </c>
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>kommune@egekom.dk</t>
+        </is>
+      </c>
+      <c r="J86" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K86" s="11" t="inlineStr"/>
+      <c r="L86" s="11" t="inlineStr">
+        <is>
           <t>Weekdays daytime plus selected Saturdays</t>
         </is>
       </c>
-      <c r="I86" s="11" t="inlineStr">
+      <c r="M86" s="11" t="inlineStr">
         <is>
           <t>Own page: earliest slot 14 days after the municipality receives the certificate, so 9-13 Oct at best</t>
         </is>
       </c>
-      <c r="J86" s="19" t="inlineStr">
+      <c r="N86" s="19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K86" s="11" t="inlineStr">
+      <c r="O86" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. S-train to Ølstykke approx 45 min.</t>
         </is>
       </c>
-      <c r="L86" s="14" t="inlineStr">
+      <c r="P86" s="14" t="inlineStr">
         <is>
           <t>https://www.egedalkommune.dk</t>
         </is>
       </c>
-      <c r="M86" s="14" t="inlineStr">
+      <c r="Q86" s="14" t="inlineStr">
         <is>
           <t>https://www.egedalkommune.dk/mit-liv/personlige-forhold/vielse</t>
         </is>
       </c>
-      <c r="N86" s="11" t="inlineStr">
+      <c r="R86" s="11" t="inlineStr">
         <is>
           <t>14-day-after-certificate rule rules the window out.</t>
         </is>
@@ -6245,35 +7923,51 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
+          <t>+45 39 98 00 00</t>
+        </is>
+      </c>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>vielse@gentofte.dk</t>
+        </is>
+      </c>
+      <c r="J87" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K87" s="11" t="inlineStr"/>
+      <c r="L87" s="11" t="inlineStr">
+        <is>
           <t>Mon, Tue, Thu approx 10:00 or 14:00; Sat 11:00</t>
         </is>
       </c>
-      <c r="I87" s="11" t="inlineStr">
+      <c r="M87" s="11" t="inlineStr">
         <is>
           <t>English page: at least 4 weeks from receipt of certificate to wedding</t>
         </is>
       </c>
-      <c r="J87" s="19" t="inlineStr">
+      <c r="N87" s="19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K87" s="11" t="inlineStr">
+      <c r="O87" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. S-train to Charlottenlund approx 25 min.</t>
         </is>
       </c>
-      <c r="L87" s="14" t="inlineStr">
+      <c r="P87" s="14" t="inlineStr">
         <is>
           <t>https://gentofte.dk</t>
         </is>
       </c>
-      <c r="M87" s="14" t="inlineStr">
+      <c r="Q87" s="14" t="inlineStr">
         <is>
           <t>https://gentofte.dk/borgerservice/vielse/aegteskab-og-vielse/</t>
         </is>
       </c>
-      <c r="N87" s="11" t="inlineStr">
+      <c r="R87" s="11" t="inlineStr">
         <is>
           <t>4-week rule rules the window out.</t>
         </is>
@@ -6311,35 +8005,51 @@
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="I88" s="11" t="inlineStr">
+        <is>
+          <t>mail@halsnaes.dk</t>
+        </is>
+      </c>
+      <c r="J88" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K88" s="11" t="inlineStr"/>
+      <c r="L88" s="11" t="inlineStr">
+        <is>
           <t>Tue-Fri 11-13; some Saturdays</t>
         </is>
       </c>
-      <c r="I88" s="11" t="inlineStr">
+      <c r="M88" s="11" t="inlineStr">
         <is>
           <t>Fully booked for non-Danish citizens without residence; not handling non-resident requests until 19 Oct 2026</t>
         </is>
       </c>
-      <c r="J88" s="19" t="inlineStr">
+      <c r="N88" s="19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K88" s="11" t="inlineStr">
+      <c r="O88" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train via Hillerød approx 1h20.</t>
         </is>
       </c>
-      <c r="L88" s="14" t="inlineStr">
+      <c r="P88" s="14" t="inlineStr">
         <is>
           <t>https://halsnaes.dk</t>
         </is>
       </c>
-      <c r="M88" s="14" t="inlineStr">
+      <c r="Q88" s="14" t="inlineStr">
         <is>
           <t>https://halsnaes.dk/borger/voksne-og-seniorer/vielse</t>
         </is>
       </c>
-      <c r="N88" s="11" t="inlineStr">
+      <c r="R88" s="11" t="inlineStr">
         <is>
           <t>Closed to non-residents until after your window.</t>
         </is>
@@ -6377,35 +8087,51 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="J89" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K89" s="11" t="inlineStr"/>
+      <c r="L89" s="11" t="inlineStr">
+        <is>
           <t>Weekdays and Saturdays</t>
         </is>
       </c>
-      <c r="I89" s="11" t="inlineStr">
+      <c r="M89" s="11" t="inlineStr">
         <is>
           <t>Approx 12 weeks wait; 40% of slots reserved for residents; express service ended May 2025</t>
         </is>
       </c>
-      <c r="J89" s="19" t="inlineStr">
+      <c r="N89" s="19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K89" s="11" t="inlineStr">
+      <c r="O89" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Metro to Rådhuspladsen 15 min.</t>
         </is>
       </c>
-      <c r="L89" s="14" t="inlineStr">
+      <c r="P89" s="14" t="inlineStr">
         <is>
           <t>https://www.kk.dk</t>
         </is>
       </c>
-      <c r="M89" s="14" t="inlineStr">
+      <c r="Q89" s="14" t="inlineStr">
         <is>
           <t>https://idocph.kk.dk/en/city-hall-wedding</t>
         </is>
       </c>
-      <c r="N89" s="11" t="inlineStr">
+      <c r="R89" s="11" t="inlineStr">
         <is>
           <t>Ruled out by waiting time.</t>
         </is>
@@ -6436,34 +8162,54 @@
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr"/>
-      <c r="G90" s="11" t="inlineStr"/>
-      <c r="H90" s="11" t="inlineStr"/>
+      <c r="G90" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="H90" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="J90" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K90" s="11" t="inlineStr"/>
+      <c r="L90" s="11" t="inlineStr"/>
+      <c r="M90" s="11" t="inlineStr">
+        <is>
           <t>Marries residents or couples with a special connection only</t>
         </is>
       </c>
-      <c r="J90" s="19" t="inlineStr">
+      <c r="N90" s="19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K90" s="11" t="inlineStr">
+      <c r="O90" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. S-train to Lyngby approx 25 min.</t>
         </is>
       </c>
-      <c r="L90" s="14" t="inlineStr">
+      <c r="P90" s="14" t="inlineStr">
         <is>
           <t>https://www.ltk.dk</t>
         </is>
       </c>
-      <c r="M90" s="14" t="inlineStr">
+      <c r="Q90" s="14" t="inlineStr">
         <is>
           <t>https://www.ltk.dk/borger/personlige-forhold/aegteskab-og-ceremonier/naar-i-vil-giftes</t>
         </is>
       </c>
-      <c r="N90" s="11" t="inlineStr">
+      <c r="R90" s="11" t="inlineStr">
         <is>
           <t>Residency restriction.</t>
         </is>
@@ -6501,35 +8247,51 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="J91" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K91" s="11" t="inlineStr"/>
+      <c r="L91" s="11" t="inlineStr">
+        <is>
           <t>Thu, Fri, Sat</t>
         </is>
       </c>
-      <c r="I91" s="11" t="inlineStr">
+      <c r="M91" s="11" t="inlineStr">
         <is>
           <t>Earliest ceremony 14 days after the municipality receives your certificate, so 9-13 Oct at best</t>
         </is>
       </c>
-      <c r="J91" s="19" t="inlineStr">
+      <c r="N91" s="19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K91" s="11" t="inlineStr">
+      <c r="O91" s="11" t="inlineStr">
         <is>
           <t>Fly London STN to Aarhus AAR (Ryanair) approx 1h45, or Billund BLL.</t>
         </is>
       </c>
-      <c r="L91" s="14" t="inlineStr">
+      <c r="P91" s="14" t="inlineStr">
         <is>
           <t>https://aarhus.dk</t>
         </is>
       </c>
-      <c r="M91" s="14" t="inlineStr">
+      <c r="Q91" s="14" t="inlineStr">
         <is>
           <t>https://international.aarhus.dk/live/citizen-service-borgerservice/getting-married/</t>
         </is>
       </c>
-      <c r="N91" s="11" t="inlineStr">
+      <c r="R91" s="11" t="inlineStr">
         <is>
           <t>14-day-after-certificate rule.</t>
         </is>
@@ -6567,35 +8329,51 @@
       </c>
       <c r="H92" s="11" t="inlineStr">
         <is>
+          <t>+45 99 74 15 72</t>
+        </is>
+      </c>
+      <c r="I92" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="J92" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K92" s="11" t="inlineStr"/>
+      <c r="L92" s="11" t="inlineStr">
+        <is>
           <t>Tue and Thu 14:00-15:30</t>
         </is>
       </c>
-      <c r="I92" s="11" t="inlineStr">
+      <c r="M92" s="11" t="inlineStr">
         <is>
           <t>Up to 3 months waiting; ID in person the day before</t>
         </is>
       </c>
-      <c r="J92" s="19" t="inlineStr">
+      <c r="N92" s="19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K92" s="11" t="inlineStr">
+      <c r="O92" s="11" t="inlineStr">
         <is>
           <t>Fly London (STN/LTN/LGW) to Billund BLL, approx 1h45. Car approx 1h15.</t>
         </is>
       </c>
-      <c r="L92" s="14" t="inlineStr">
+      <c r="P92" s="14" t="inlineStr">
         <is>
           <t>https://www.rksk.dk</t>
         </is>
       </c>
-      <c r="M92" s="14" t="inlineStr">
+      <c r="Q92" s="14" t="inlineStr">
         <is>
           <t>https://www.rksk.dk/borger/borgerservice/vielse</t>
         </is>
       </c>
-      <c r="N92" s="11" t="inlineStr"/>
+      <c r="R92" s="11" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="11" t="n">
@@ -6629,31 +8407,47 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="I93" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="J93" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K93" s="11" t="inlineStr"/>
+      <c r="L93" s="11" t="inlineStr">
+        <is>
           <t>3 days a week</t>
         </is>
       </c>
-      <c r="I93" s="11" t="inlineStr">
+      <c r="M93" s="11" t="inlineStr">
         <is>
           <t>Slots released 60 days ahead and go fast; earliest 14 days after certificate</t>
         </is>
       </c>
-      <c r="J93" s="19" t="inlineStr">
+      <c r="N93" s="19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K93" s="11" t="inlineStr">
+      <c r="O93" s="11" t="inlineStr">
         <is>
           <t>Fly London to Copenhagen CPH then 45 min hop to Aalborg AAL, or Billund BLL then approx 2h drive.</t>
         </is>
       </c>
-      <c r="L93" s="14" t="inlineStr">
+      <c r="P93" s="14" t="inlineStr">
         <is>
           <t>https://www.aalborg.dk</t>
         </is>
       </c>
-      <c r="M93" s="11" t="inlineStr"/>
-      <c r="N93" s="11" t="inlineStr">
+      <c r="Q93" s="11" t="inlineStr"/>
+      <c r="R93" s="11" t="inlineStr">
         <is>
           <t>14-day-after-certificate rule.</t>
         </is>
@@ -6696,26 +8490,42 @@
       </c>
       <c r="I94" s="11" t="inlineStr">
         <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="J94" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K94" s="11" t="inlineStr"/>
+      <c r="L94" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="M94" s="11" t="inlineStr">
+        <is>
           <t>3-4 weeks after receiving an external certificate</t>
         </is>
       </c>
-      <c r="J94" s="19" t="inlineStr">
+      <c r="N94" s="19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K94" s="11" t="inlineStr">
+      <c r="O94" s="11" t="inlineStr">
         <is>
           <t>Fly London (LHR/LGW/STN/LTN) to Copenhagen CPH, approx 1h50. Train to Roskilde approx 25 min.</t>
         </is>
       </c>
-      <c r="L94" s="14" t="inlineStr">
+      <c r="P94" s="14" t="inlineStr">
         <is>
           <t>https://www.roskilde.dk</t>
         </is>
       </c>
-      <c r="M94" s="11" t="inlineStr"/>
-      <c r="N94" s="11" t="inlineStr">
+      <c r="Q94" s="11" t="inlineStr"/>
+      <c r="R94" s="11" t="inlineStr">
         <is>
           <t>Too slow for the window.</t>
         </is>
@@ -6757,35 +8567,51 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="I95" s="11" t="inlineStr">
+        <is>
+          <t>vielser@aabenraa.dk</t>
+        </is>
+      </c>
+      <c r="J95" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K95" s="11" t="inlineStr"/>
+      <c r="L95" s="11" t="inlineStr">
+        <is>
           <t>Mon-Thu 10-12 with council witnesses; any day except Sunday with own witnesses</t>
         </is>
       </c>
-      <c r="I95" s="11" t="inlineStr">
+      <c r="M95" s="11" t="inlineStr">
         <is>
           <t>AUTO-REPLY 17 Sep: always fully booked at least 2 months ahead; replies take 1-2 weeks</t>
         </is>
       </c>
-      <c r="J95" s="19" t="inlineStr">
+      <c r="N95" s="19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K95" s="11" t="inlineStr">
+      <c r="O95" s="11" t="inlineStr">
         <is>
           <t>Fly London (STN/LTN/LGW) to Billund BLL, approx 1h45. Car approx 1h. Alternative: fly London to Hamburg HAM approx 1h30, then train/car north approx 1h30 to 2h.</t>
         </is>
       </c>
-      <c r="L95" s="14" t="inlineStr">
+      <c r="P95" s="14" t="inlineStr">
         <is>
           <t>https://aabenraa.dk</t>
         </is>
       </c>
-      <c r="M95" s="14" t="inlineStr">
+      <c r="Q95" s="14" t="inlineStr">
         <is>
           <t>https://aabenraa.dk/borger/boern-og-familie/vielse-og-skilsmisse/vielse</t>
         </is>
       </c>
-      <c r="N95" s="11" t="inlineStr">
+      <c r="R95" s="11" t="inlineStr">
         <is>
           <t>Email sent; effectively answered no.</t>
         </is>
@@ -6827,35 +8653,51 @@
       </c>
       <c r="H96" s="11" t="inlineStr">
         <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="I96" s="11" t="inlineStr">
+        <is>
+          <t>vielse@esbjerg.dk</t>
+        </is>
+      </c>
+      <c r="J96" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K96" s="11" t="inlineStr"/>
+      <c r="L96" s="11" t="inlineStr">
+        <is>
           <t>International couples: Fridays (alternating Ribe/Esbjerg), Saturdays with own witnesses</t>
         </is>
       </c>
-      <c r="I96" s="11" t="inlineStr">
+      <c r="M96" s="11" t="inlineStr">
         <is>
           <t>AUTO-REPLY 17 Sep: no short-term slots, next appointments from January 2027</t>
         </is>
       </c>
-      <c r="J96" s="19" t="inlineStr">
+      <c r="N96" s="19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K96" s="11" t="inlineStr">
+      <c r="O96" s="11" t="inlineStr">
         <is>
           <t>Fly London (STN/LTN/LGW) to Billund BLL, approx 1h45. Car/train approx 1h.</t>
         </is>
       </c>
-      <c r="L96" s="14" t="inlineStr">
+      <c r="P96" s="14" t="inlineStr">
         <is>
           <t>https://www.esbjerg.dk</t>
         </is>
       </c>
-      <c r="M96" s="14" t="inlineStr">
+      <c r="Q96" s="14" t="inlineStr">
         <is>
           <t>https://www.esbjerg.dk/personlige-forhold/a-civil-wedding-ceremony</t>
         </is>
       </c>
-      <c r="N96" s="11" t="inlineStr">
+      <c r="R96" s="11" t="inlineStr">
         <is>
           <t>Email sent; answered no.</t>
         </is>
@@ -6893,31 +8735,51 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
+          <t>74 34 34 34</t>
+        </is>
+      </c>
+      <c r="I97" s="11" t="inlineStr">
+        <is>
+          <t>post@haderslev.dk</t>
+        </is>
+      </c>
+      <c r="J97" s="11" t="inlineStr">
+        <is>
+          <t>Haderslev Rådhus, Gåskærgade 26, 6100 Haderslev</t>
+        </is>
+      </c>
+      <c r="K97" s="14" t="inlineStr">
+        <is>
+          <t>https://www.haderslev.dk/om-kommunen/kontakt-og-aabningstider</t>
+        </is>
+      </c>
+      <c r="L97" s="11" t="inlineStr">
+        <is>
           <t>Fri 10-12, Sat 10-12</t>
         </is>
       </c>
-      <c r="I97" s="11" t="inlineStr">
+      <c r="M97" s="11" t="inlineStr">
         <is>
           <t>DR reported 'fully booked for the rest of the year'</t>
         </is>
       </c>
-      <c r="J97" s="19" t="inlineStr">
+      <c r="N97" s="19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K97" s="11" t="inlineStr">
+      <c r="O97" s="11" t="inlineStr">
         <is>
           <t>Fly London (STN/LTN/LGW) to Billund BLL, approx 1h45. Car approx 1h. Alternative: fly London to Hamburg HAM approx 1h30, then train/car north approx 1h30 to 2h.</t>
         </is>
       </c>
-      <c r="L97" s="14" t="inlineStr">
+      <c r="P97" s="14" t="inlineStr">
         <is>
           <t>https://www.haderslev.dk</t>
         </is>
       </c>
-      <c r="M97" s="11" t="inlineStr"/>
-      <c r="N97" s="11" t="inlineStr"/>
+      <c r="Q97" s="11" t="inlineStr"/>
+      <c r="R97" s="11" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="11" t="n">
@@ -6951,35 +8813,51 @@
       </c>
       <c r="H98" s="11" t="inlineStr">
         <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="J98" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K98" s="11" t="inlineStr"/>
+      <c r="L98" s="11" t="inlineStr">
+        <is>
           <t>Fridays only</t>
         </is>
       </c>
-      <c r="I98" s="11" t="inlineStr">
+      <c r="M98" s="11" t="inlineStr">
         <is>
           <t>Next free date reported 20 Nov 2026</t>
         </is>
       </c>
-      <c r="J98" s="19" t="inlineStr">
+      <c r="N98" s="19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K98" s="11" t="inlineStr">
+      <c r="O98" s="11" t="inlineStr">
         <is>
           <t>Fly London (STN/LTN/LGW) to Billund BLL, approx 1h45. Car approx 1h20. Alternative: fly London to Hamburg HAM approx 1h30, then train/car north approx 1h30 to 2h.</t>
         </is>
       </c>
-      <c r="L98" s="14" t="inlineStr">
+      <c r="P98" s="14" t="inlineStr">
         <is>
           <t>https://sonderborgkommune.dk</t>
         </is>
       </c>
-      <c r="M98" s="14" t="inlineStr">
+      <c r="Q98" s="14" t="inlineStr">
         <is>
           <t>https://sonderborgkommune.dk/en/wedding</t>
         </is>
       </c>
-      <c r="N98" s="11" t="inlineStr"/>
+      <c r="R98" s="11" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="11" t="n">
@@ -7006,180 +8884,730 @@
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr"/>
-      <c r="G99" s="11" t="inlineStr"/>
-      <c r="H99" s="11" t="inlineStr"/>
+      <c r="G99" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="H99" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="J99" s="11" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="K99" s="11" t="inlineStr"/>
+      <c r="L99" s="11" t="inlineStr"/>
+      <c r="M99" s="11" t="inlineStr">
+        <is>
           <t>Booked 2-3 months ahead</t>
         </is>
       </c>
-      <c r="J99" s="19" t="inlineStr">
+      <c r="N99" s="19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K99" s="11" t="inlineStr">
+      <c r="O99" s="11" t="inlineStr">
         <is>
           <t>Fly London (STN/LTN/LGW) to Billund BLL, approx 1h45. Car approx 1h15. Alternative: fly London to Hamburg HAM approx 1h30, then train/car north approx 1h30 to 2h.</t>
         </is>
       </c>
-      <c r="L99" s="14" t="inlineStr">
+      <c r="P99" s="14" t="inlineStr">
         <is>
           <t>https://toender.dk</t>
         </is>
       </c>
-      <c r="M99" s="11" t="inlineStr"/>
-      <c r="N99" s="11" t="inlineStr">
+      <c r="Q99" s="11" t="inlineStr"/>
+      <c r="R99" s="11" t="inlineStr">
         <is>
           <t>Busiest wedding town in Denmark.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N99"/>
+  <autoFilter ref="A1:R99"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L76" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M79" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L81" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L82" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M82" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L83" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L84" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M84" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L85" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M85" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L86" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M86" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L87" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M87" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L88" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M88" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L89" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M89" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L90" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M90" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M91" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M92" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L93" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M95" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M96" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M98" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q29" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q41" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P45" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q45" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q46" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q47" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P52" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P53" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P54" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P55" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P56" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P57" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P58" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P59" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P60" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P61" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P62" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P63" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P64" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P65" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P66" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P67" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P68" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P69" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P70" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P71" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P72" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P73" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P74" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q74" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P75" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P76" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q76" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P77" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P78" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P79" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q79" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P80" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q80" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P81" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q81" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P82" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q82" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P83" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K84" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P84" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q84" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P85" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q85" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P86" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q86" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P87" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q87" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P88" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q88" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P89" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q89" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P90" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q90" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P91" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q91" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P92" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q92" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P93" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P94" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P95" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q95" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P96" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q96" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P97" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P98" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q98" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P99" r:id="rId212"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Agency</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>Phone / WhatsApp</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>What they offer / price notes</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="inlineStr">
+        <is>
+          <t>Quote request status (17 Sep 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>Wedding Planner Denmark</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t>https://www.weddingplannerdenmark.com/contact/</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>info@weddingplannerdenmark.com</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>+45 52 72 38 96 (WhatsApp), 8am-10pm daily</t>
+        </is>
+      </c>
+      <c r="E2" s="20" t="inlineStr">
+        <is>
+          <t>Copenhagen area</t>
+        </is>
+      </c>
+      <c r="F2" s="20" t="inlineStr">
+        <is>
+          <t>30+ town halls; express service typically within 8 weeks using private venues; Familieretshuset fee EUR 282 included in most packages</t>
+        </is>
+      </c>
+      <c r="G2" s="20" t="inlineStr">
+        <is>
+          <t>Quote request sent</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>Getting Married in Denmark</t>
+        </is>
+      </c>
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t>https://gettingmarriedindenmark.com/</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>Contact@gettingmarriedindenmark.com</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr"/>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>Købmagergade 61a, Copenhagen</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>Files the application and coordinates with town halls; support levels vary by package</t>
+        </is>
+      </c>
+      <c r="G3" s="20" t="inlineStr">
+        <is>
+          <t>Quote request sent</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Marry Abroad Simply</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>https://marryabroadsimply.com/contact</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>interest@marryabroadsimply.com</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>+45 71 49 34 83 (WhatsApp), Mon-Fri 10-17</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>Østerbrogade 226, Copenhagen</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>Venues include Lolland/Maribo, Vordingborg, Stevns, Albertslund, Bornholm; express weddings via agency slots</t>
+        </is>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>Quote request sent</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Denmark Marriage Service</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>https://denmarkmarriageservice.com/</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>info@denmarkmarriageservice.dk</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>Odense</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>From EUR 179; documents, legalisation and apostille; replies within 24h</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>Quote request sent</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>Easy Weddings Denmark</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>https://easyweddingsdenmark.com/</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>info@easyweddingsdenmark.com</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>+45 52 60 52 36</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>Copenhagen</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>Packages Essential / Complete / Priority / Premium; same-day marriage page; same phone as Denmark Wedding Agency</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>Draft in Gmail, please send</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>BINELI</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>https://bineli.de/en/contacts/</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>mail@bineli.de</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>+49 155 689 703 57 (Viber/WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>Hamburg, Germany</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>EUR 125 service fee plus urgent surcharge EUR 80 (30 days or less) to EUR 280 (10 days or less)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>Draft in Gmail, please send</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>Nordic Adventure Weddings</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>https://www.nordicadventureweddings.eu/contact</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>web form</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>+45 31 89 92 56</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>Kaj Munks Gade 1, Maribo (next to Maribo Town Hall)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>Town hall package EUR 780, no residency needed; express timeline page</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>Phone or web form</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>Denmark Wedding Services</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>https://denmarkweddingservices.com/en</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>web form</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>Comfort package EUR 799.99 all-in including Danish fees; EUR 19.99 video consultation</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>Web form</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>Wedding in Denmark</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>https://weddingindenmark.dk/contact/</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>web form</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>Express service within 8 weeks at private venues; SOS service</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>Web form</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Just Married in Denmark</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>https://justmarriedindenmark.com/contact/</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>info@justmarriedindenmark.com</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>+45 52 72 38 96</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>Vallensbæk Strand</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>Part of Wedding Planner Denmark; approvals often within 5 working days</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>Covered by Wedding Planner Denmark request</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>Dänemark Heiraten</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>https://daenemarkheiraten.de/en/packages-and-prices/</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>not found</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>EUR 1,650 including the EUR 240 state fee</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Denmark_wedding_municipalities_2026.xlsx
+++ b/Denmark_wedding_municipalities_2026.xlsx
@@ -4056,12 +4056,12 @@
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>post@holb.dk</t>
         </is>
       </c>
       <c r="J39" s="11" t="inlineStr">
         <is>
-          <t>Jernbanevej 6, 4300 Holbæk</t>
+          <t>Kanalstræde 2, 4300 Holbæk</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
@@ -6069,20 +6069,24 @@
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>99 66 70 00</t>
         </is>
       </c>
       <c r="I64" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>post@vesthimmerland.dk</t>
         </is>
       </c>
       <c r="J64" s="11" t="inlineStr">
         <is>
-          <t>not found</t>
-        </is>
-      </c>
-      <c r="K64" s="11" t="inlineStr"/>
+          <t>Vestre Boulevard 7, 9600 Aars</t>
+        </is>
+      </c>
+      <c r="K64" s="14" t="inlineStr">
+        <is>
+          <t>https://vesthimmerland.dk/kontakt</t>
+        </is>
+      </c>
       <c r="L64" s="11" t="inlineStr">
         <is>
           <t>not found</t>
@@ -9077,77 +9081,78 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P62" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P63" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P64" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P65" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P66" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P67" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P68" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P69" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P70" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P71" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P72" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P73" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P74" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q74" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P75" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P76" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q76" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P77" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P78" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P79" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q79" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P80" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q80" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P81" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q81" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P82" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q82" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P83" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K84" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P84" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q84" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P85" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q85" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P86" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q86" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P87" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q87" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P88" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q88" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P89" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q89" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P90" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q90" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P91" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q91" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P92" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q92" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P93" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P94" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P95" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q95" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P96" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q96" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P97" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P98" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q98" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P99" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P64" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P65" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P66" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P67" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P68" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P69" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P70" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P71" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P72" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P73" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P74" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q74" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P75" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P76" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q76" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P77" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P78" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P79" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q79" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P80" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q80" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P81" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q81" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P82" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q82" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P83" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K84" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P84" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q84" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P85" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q85" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P86" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q86" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P87" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q87" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P88" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q88" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P89" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q89" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P90" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q90" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P91" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q91" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P92" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q92" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P93" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P94" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P95" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q95" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P96" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q96" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P97" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P98" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q98" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P99" r:id="rId213"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Denmark_wedding_municipalities_2026.xlsx
+++ b/Denmark_wedding_municipalities_2026.xlsx
@@ -1001,7 +1001,11 @@
           <t>Emailed (sent)</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr"/>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>NO (17 Sep): no free slots before the end of the year</t>
+        </is>
+      </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
           <t>borgerogydelsescenter@albertslund.dk / +45 43 68 68 68</t>
@@ -1083,7 +1087,11 @@
           <t>Emailed (sent)</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr"/>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>Auto-reply 17 Sep: received</t>
+        </is>
+      </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
           <t>vielse@brondby.dk</t>
@@ -1247,7 +1255,11 @@
           <t>Emailed (sent)</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr"/>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>Auto-reply 17 Sep: handled within 10 working days</t>
+        </is>
+      </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
           <t>borgerservice@gribskov.dk / +45 72 49 60 00</t>
@@ -1329,7 +1341,11 @@
           <t>Emailed (sent)</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr"/>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>NO (17 Sep): fully booked until December 2026</t>
+        </is>
+      </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
           <t>borgerservice@helsingor.dk</t>
@@ -1493,7 +1509,11 @@
           <t>Emailed (sent)</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr"/>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>Auto-reply 17 Sep: forwarded to the right department</t>
+        </is>
+      </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
           <t>skanderborg.kommune@skanderborg.dk / wedding booking +45 87 94 74 67</t>
@@ -1575,7 +1595,11 @@
           <t>Emailed (sent)</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr"/>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>NO (17 Sep): no available dates until February 2027</t>
+        </is>
+      </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
           <t>borgerservice@lolland.dk / +45 54 67 67 67</t>
@@ -1653,7 +1677,11 @@
           <t>Emailed (sent)</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr"/>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>NO (17 Sep): fully booked September, October and early November</t>
+        </is>
+      </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
           <t>vardekommune@varde.dk / +45 79 94 68 00</t>
@@ -7753,7 +7781,7 @@
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>Auto-reply: answer within 3-5 working days</t>
+          <t>Auto-reply 17 Sep: answer within 3-5 working days</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
@@ -8561,7 +8589,7 @@
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>Auto-reply: fully booked 2+ months, reply in 1-2 weeks</t>
+          <t>Auto-reply 17 Sep: fully booked 2+ months, reply in 1-2 weeks</t>
         </is>
       </c>
       <c r="G95" s="11" t="inlineStr">
@@ -8647,7 +8675,7 @@
       </c>
       <c r="F96" s="11" t="inlineStr">
         <is>
-          <t>Auto-reply: no slots until January 2027</t>
+          <t>NO (auto-reply 17 Sep): no slots until January 2027</t>
         </is>
       </c>
       <c r="G96" s="11" t="inlineStr">
@@ -9246,7 +9274,7 @@
       </c>
       <c r="G2" s="20" t="inlineStr">
         <is>
-          <t>Quote request sent</t>
+          <t>REPLIED 17 Sep: offers Wed 7 Oct, private registrar at a seaside hotel approx 1h south of Copenhagen Airport, EUR 1,395 all-in (Familieretshuset fee, venue, registrar, witnesses, certificates). Hold requested.</t>
         </is>
       </c>
     </row>
@@ -9279,7 +9307,7 @@
       </c>
       <c r="G3" s="20" t="inlineStr">
         <is>
-          <t>Quote request sent</t>
+          <t>REPLIED 17 Sep: no town hall availability in the window; earliest end Nov / early Dec</t>
         </is>
       </c>
     </row>
@@ -9316,7 +9344,7 @@
       </c>
       <c r="G4" s="20" t="inlineStr">
         <is>
-          <t>Quote request sent</t>
+          <t>Auto-reply 17 Sep: will respond within 24 hours</t>
         </is>
       </c>
     </row>
@@ -9349,7 +9377,7 @@
       </c>
       <c r="G5" s="20" t="inlineStr">
         <is>
-          <t>Quote request sent</t>
+          <t>REPLIED 17 Sep: no dates 28 Sep-7 Oct; earliest mid/late Nov; full service EUR 850</t>
         </is>
       </c>
     </row>

--- a/Denmark_wedding_municipalities_2026.xlsx
+++ b/Denmark_wedding_municipalities_2026.xlsx
@@ -9274,7 +9274,7 @@
       </c>
       <c r="G2" s="20" t="inlineStr">
         <is>
-          <t>REPLIED 17 Sep: offers Wed 7 Oct, private registrar at a seaside hotel approx 1h south of Copenhagen Airport, EUR 1,395 all-in (Familieretshuset fee, venue, registrar, witnesses, certificates). Hold requested.</t>
+          <t>Auto-reply 17 Sep: will respond within 24 hours</t>
         </is>
       </c>
     </row>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="G4" s="20" t="inlineStr">
         <is>
-          <t>Auto-reply 17 Sep: will respond within 24 hours</t>
+          <t>REPLIED 17 Sep: offers Wed 7 Oct, private registrar at a seaside hotel approx 1h south of Copenhagen Airport, EUR 1,395 all-in (Familieretshuset fee, venue, registrar, witnesses, certificates). Hold requested.</t>
         </is>
       </c>
     </row>

--- a/Denmark_wedding_municipalities_2026.xlsx
+++ b/Denmark_wedding_municipalities_2026.xlsx
@@ -2000,9 +2000,9 @@
           <t>Frederikssund, 40 km NW of Copenhagen</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>Not contacted</t>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>Emailed (sent)</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr"/>
